--- a/設計書.xlsx
+++ b/設計書.xlsx
@@ -8,12 +8,13 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\ikura\次世代開発\ソース\CounterServer\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1C78FB3F-23A4-4672-BCD3-71F06EDE29A8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BF3EE5A8-155F-47F8-B442-9FFEBDCA63E3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="レイアウト" sheetId="1" r:id="rId1"/>
+    <sheet name="設計書_距離" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -25,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="7">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="63" uniqueCount="53">
   <si>
     <t>Home</t>
     <phoneticPr fontId="1"/>
@@ -58,6 +59,459 @@
   </si>
   <si>
     <t>Update</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>概要</t>
+    <rPh sb="0" eb="2">
+      <t>ガイヨウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>箱に溜まった部品との距離に応じて製品が一杯になったことを通知する。</t>
+    <rPh sb="0" eb="1">
+      <t>ハコ</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>タ</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>ブヒン</t>
+    </rPh>
+    <rPh sb="10" eb="12">
+      <t>キョリ</t>
+    </rPh>
+    <rPh sb="13" eb="14">
+      <t>オウ</t>
+    </rPh>
+    <rPh sb="16" eb="18">
+      <t>セイヒン</t>
+    </rPh>
+    <rPh sb="19" eb="21">
+      <t>イッパイ</t>
+    </rPh>
+    <rPh sb="28" eb="30">
+      <t>ツウチ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>通知の方法</t>
+    <rPh sb="0" eb="2">
+      <t>ツウチ</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>ホウホウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>検知の方法</t>
+    <rPh sb="0" eb="2">
+      <t>ケンチ</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>ホウホウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>製品との距離が近い状態が指定された秒数を経過したときに、一杯になったことを通知する</t>
+    <rPh sb="0" eb="2">
+      <t>セイヒン</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>キョリ</t>
+    </rPh>
+    <rPh sb="7" eb="8">
+      <t>チカ</t>
+    </rPh>
+    <rPh sb="9" eb="11">
+      <t>ジョウタイ</t>
+    </rPh>
+    <rPh sb="12" eb="14">
+      <t>シテイ</t>
+    </rPh>
+    <rPh sb="17" eb="19">
+      <t>ビョウスウ</t>
+    </rPh>
+    <rPh sb="20" eb="22">
+      <t>ケイカ</t>
+    </rPh>
+    <rPh sb="28" eb="30">
+      <t>イッパイ</t>
+    </rPh>
+    <rPh sb="37" eb="39">
+      <t>ツウチ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>※距離と経過時間は、レーンごとに設定ファイルにより定義</t>
+    <rPh sb="1" eb="3">
+      <t>キョリ</t>
+    </rPh>
+    <rPh sb="4" eb="8">
+      <t>ケイカジカン</t>
+    </rPh>
+    <rPh sb="16" eb="18">
+      <t>セッテイ</t>
+    </rPh>
+    <rPh sb="25" eb="27">
+      <t>テイギ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>通知内容</t>
+    <rPh sb="0" eb="2">
+      <t>ツウチ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>ナイヨウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>現状、プッシュ通知ができないため、Webの画面にて通知を行う。</t>
+    <rPh sb="0" eb="2">
+      <t>ゲンジョウ</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>ツウチ</t>
+    </rPh>
+    <rPh sb="21" eb="23">
+      <t>ガメン</t>
+    </rPh>
+    <rPh sb="25" eb="27">
+      <t>ツウチ</t>
+    </rPh>
+    <rPh sb="28" eb="29">
+      <t>オコナ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>通常</t>
+    <rPh sb="0" eb="2">
+      <t>ツウジョウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>一杯になったことを示す通知</t>
+    <rPh sb="0" eb="2">
+      <t>イッパイ</t>
+    </rPh>
+    <rPh sb="9" eb="10">
+      <t>シメ</t>
+    </rPh>
+    <rPh sb="11" eb="13">
+      <t>ツウチ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>※通知を消す場合は、Resetボタンをクリックする。または、基板についているリセットボタンを押す。</t>
+    <rPh sb="1" eb="3">
+      <t>ツウチ</t>
+    </rPh>
+    <rPh sb="4" eb="5">
+      <t>ケ</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>バアイ</t>
+    </rPh>
+    <rPh sb="30" eb="32">
+      <t>キバン</t>
+    </rPh>
+    <rPh sb="46" eb="47">
+      <t>オ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>詳細</t>
+    <rPh sb="0" eb="2">
+      <t>ショウサイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>RaspberryPi Pico 側の動作</t>
+    <rPh sb="17" eb="18">
+      <t>ガワ</t>
+    </rPh>
+    <rPh sb="19" eb="21">
+      <t>ドウサ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>現在の距離をサーバへ送る処理</t>
+    <rPh sb="0" eb="2">
+      <t>ゲンザイ</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>キョリ</t>
+    </rPh>
+    <rPh sb="10" eb="11">
+      <t>オク</t>
+    </rPh>
+    <rPh sb="12" eb="14">
+      <t>ショリ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>・</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>0.5秒に１回送信する</t>
+    <rPh sb="3" eb="4">
+      <t>ビョウ</t>
+    </rPh>
+    <rPh sb="6" eb="7">
+      <t>カイ</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>ソウシン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>送信JSON</t>
+    <rPh sb="0" eb="2">
+      <t>ソウシン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>no : n</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>dist : m</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>}</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>{</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>レーン番号</t>
+    <rPh sb="3" eb="5">
+      <t>バンゴウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>距離</t>
+    <rPh sb="0" eb="2">
+      <t>キョリ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>CounterServerの動作</t>
+    <rPh sb="14" eb="16">
+      <t>ドウサ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>距離情報を受け取ったとき</t>
+    <rPh sb="0" eb="4">
+      <t>キョリジョウホウ</t>
+    </rPh>
+    <rPh sb="5" eb="6">
+      <t>ウ</t>
+    </rPh>
+    <rPh sb="7" eb="8">
+      <t>ト</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>DBへ保存</t>
+  </si>
+  <si>
+    <t>no</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>dist</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>②</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>①</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>DBの内容を見て、指定距離以下に指定秒の状態を判定する。</t>
+    <rPh sb="3" eb="5">
+      <t>ナイヨウ</t>
+    </rPh>
+    <rPh sb="6" eb="7">
+      <t>ミ</t>
+    </rPh>
+    <rPh sb="9" eb="13">
+      <t>シテイキョリ</t>
+    </rPh>
+    <rPh sb="13" eb="15">
+      <t>イカ</t>
+    </rPh>
+    <rPh sb="16" eb="19">
+      <t>シテイビョウ</t>
+    </rPh>
+    <rPh sb="20" eb="22">
+      <t>ジョウタイ</t>
+    </rPh>
+    <rPh sb="23" eb="25">
+      <t>ハンテイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>sec : l</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>秒</t>
+    <rPh sb="0" eb="1">
+      <t>ビョウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>sec</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>savetime</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>指定距離以下になっているレコードのsecの合計時間を算出</t>
+    <rPh sb="0" eb="4">
+      <t>シテイキョリ</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>イカ</t>
+    </rPh>
+    <rPh sb="21" eb="25">
+      <t>ゴウケイジカン</t>
+    </rPh>
+    <rPh sb="26" eb="28">
+      <t>サンシュツ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>nレーンにおいて、現在から指定秒以内のレコードを選択</t>
+    <rPh sb="9" eb="11">
+      <t>ゲンザイ</t>
+    </rPh>
+    <rPh sb="13" eb="15">
+      <t>シテイ</t>
+    </rPh>
+    <rPh sb="15" eb="16">
+      <t>ビョウ</t>
+    </rPh>
+    <rPh sb="16" eb="18">
+      <t>イナイ</t>
+    </rPh>
+    <rPh sb="24" eb="26">
+      <t>センタク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>③</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>no : レーン番号</t>
+    <rPh sb="8" eb="10">
+      <t>バンゴウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>算出時間に応じて通知を送信する</t>
+    <rPh sb="0" eb="2">
+      <t>サンシュツ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>ジカン</t>
+    </rPh>
+    <rPh sb="5" eb="6">
+      <t>オウ</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>ツウチ</t>
+    </rPh>
+    <rPh sb="11" eb="13">
+      <t>ソウシン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>指定秒以上の場合</t>
+    <rPh sb="0" eb="3">
+      <t>シテイビョウ</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>イジョウ</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>バアイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>指定秒未満の場合</t>
+    <rPh sb="0" eb="3">
+      <t>シテイビョウ</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>ミマン</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>バアイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>type : "lenge"</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>lenge : 最新の距離</t>
+    <rPh sb="8" eb="10">
+      <t>サイシン</t>
+    </rPh>
+    <rPh sb="11" eb="13">
+      <t>キョリ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>alert : "full"</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>alert : ""</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -65,7 +519,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2">
+  <fonts count="3">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -80,13 +534,28 @@
       <charset val="128"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Yu Gothic"/>
+      <family val="3"/>
+      <charset val="128"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="12">
@@ -218,7 +687,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
@@ -228,10 +697,14 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="標準" xfId="0" builtinId="0"/>
@@ -247,6 +720,1925 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>238125</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>85725</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>9525</xdr:colOff>
+      <xdr:row>15</xdr:row>
+      <xdr:rowOff>9525</xdr:rowOff>
+    </xdr:to>
+    <xdr:grpSp>
+      <xdr:nvGrpSpPr>
+        <xdr:cNvPr id="12" name="グループ化 11">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8F0A3329-A92D-2FD4-F2B2-9DC377B22AE0}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGrpSpPr/>
+      </xdr:nvGrpSpPr>
+      <xdr:grpSpPr>
+        <a:xfrm>
+          <a:off x="733425" y="1504950"/>
+          <a:ext cx="1752600" cy="2066925"/>
+          <a:chOff x="485775" y="800100"/>
+          <a:chExt cx="1752600" cy="2066925"/>
+        </a:xfrm>
+      </xdr:grpSpPr>
+      <xdr:sp macro="" textlink="">
+        <xdr:nvSpPr>
+          <xdr:cNvPr id="2" name="テキスト ボックス 1">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{159DAECC-2BBF-ADF3-0F13-AD511E3DFDC0}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvSpPr txBox="1"/>
+        </xdr:nvSpPr>
+        <xdr:spPr>
+          <a:xfrm>
+            <a:off x="523875" y="800100"/>
+            <a:ext cx="1695450" cy="304800"/>
+          </a:xfrm>
+          <a:prstGeom prst="rect">
+            <a:avLst/>
+          </a:prstGeom>
+          <a:solidFill>
+            <a:schemeClr val="accent2">
+              <a:lumMod val="40000"/>
+              <a:lumOff val="60000"/>
+            </a:schemeClr>
+          </a:solidFill>
+          <a:ln w="9525" cmpd="sng">
+            <a:solidFill>
+              <a:schemeClr val="lt1">
+                <a:shade val="50000"/>
+              </a:schemeClr>
+            </a:solidFill>
+          </a:ln>
+        </xdr:spPr>
+        <xdr:style>
+          <a:lnRef idx="0">
+            <a:scrgbClr r="0" g="0" b="0"/>
+          </a:lnRef>
+          <a:fillRef idx="0">
+            <a:scrgbClr r="0" g="0" b="0"/>
+          </a:fillRef>
+          <a:effectRef idx="0">
+            <a:scrgbClr r="0" g="0" b="0"/>
+          </a:effectRef>
+          <a:fontRef idx="minor">
+            <a:schemeClr val="dk1"/>
+          </a:fontRef>
+        </xdr:style>
+        <xdr:txBody>
+          <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="ctr"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr algn="ctr"/>
+            <a:r>
+              <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+              <a:t>センサー</a:t>
+            </a:r>
+          </a:p>
+        </xdr:txBody>
+      </xdr:sp>
+      <xdr:cxnSp macro="">
+        <xdr:nvCxnSpPr>
+          <xdr:cNvPr id="4" name="直線コネクタ 3">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{51E42697-FD6E-F500-B1FD-C663CFB75120}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvCxnSpPr/>
+        </xdr:nvCxnSpPr>
+        <xdr:spPr>
+          <a:xfrm>
+            <a:off x="485775" y="1438275"/>
+            <a:ext cx="0" cy="1428750"/>
+          </a:xfrm>
+          <a:prstGeom prst="line">
+            <a:avLst/>
+          </a:prstGeom>
+        </xdr:spPr>
+        <xdr:style>
+          <a:lnRef idx="1">
+            <a:schemeClr val="accent1"/>
+          </a:lnRef>
+          <a:fillRef idx="0">
+            <a:schemeClr val="accent1"/>
+          </a:fillRef>
+          <a:effectRef idx="0">
+            <a:schemeClr val="accent1"/>
+          </a:effectRef>
+          <a:fontRef idx="minor">
+            <a:schemeClr val="tx1"/>
+          </a:fontRef>
+        </xdr:style>
+      </xdr:cxnSp>
+      <xdr:cxnSp macro="">
+        <xdr:nvCxnSpPr>
+          <xdr:cNvPr id="6" name="直線コネクタ 5">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6E5B83A4-014A-4F71-0882-441D7085A083}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvCxnSpPr/>
+        </xdr:nvCxnSpPr>
+        <xdr:spPr>
+          <a:xfrm flipH="1">
+            <a:off x="485775" y="2867025"/>
+            <a:ext cx="1752600" cy="0"/>
+          </a:xfrm>
+          <a:prstGeom prst="line">
+            <a:avLst/>
+          </a:prstGeom>
+        </xdr:spPr>
+        <xdr:style>
+          <a:lnRef idx="1">
+            <a:schemeClr val="accent1"/>
+          </a:lnRef>
+          <a:fillRef idx="0">
+            <a:schemeClr val="accent1"/>
+          </a:fillRef>
+          <a:effectRef idx="0">
+            <a:schemeClr val="accent1"/>
+          </a:effectRef>
+          <a:fontRef idx="minor">
+            <a:schemeClr val="tx1"/>
+          </a:fontRef>
+        </xdr:style>
+      </xdr:cxnSp>
+      <xdr:cxnSp macro="">
+        <xdr:nvCxnSpPr>
+          <xdr:cNvPr id="8" name="直線コネクタ 7">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3AE7BF50-81C2-A8C9-C1A7-92FB6A4637F8}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvCxnSpPr/>
+        </xdr:nvCxnSpPr>
+        <xdr:spPr>
+          <a:xfrm flipV="1">
+            <a:off x="2238375" y="1447800"/>
+            <a:ext cx="0" cy="1419225"/>
+          </a:xfrm>
+          <a:prstGeom prst="line">
+            <a:avLst/>
+          </a:prstGeom>
+        </xdr:spPr>
+        <xdr:style>
+          <a:lnRef idx="1">
+            <a:schemeClr val="accent1"/>
+          </a:lnRef>
+          <a:fillRef idx="0">
+            <a:schemeClr val="accent1"/>
+          </a:fillRef>
+          <a:effectRef idx="0">
+            <a:schemeClr val="accent1"/>
+          </a:effectRef>
+          <a:fontRef idx="minor">
+            <a:schemeClr val="tx1"/>
+          </a:fontRef>
+        </xdr:style>
+      </xdr:cxnSp>
+    </xdr:grpSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>238125</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>85725</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>22</xdr:col>
+      <xdr:colOff>9525</xdr:colOff>
+      <xdr:row>15</xdr:row>
+      <xdr:rowOff>9525</xdr:rowOff>
+    </xdr:to>
+    <xdr:grpSp>
+      <xdr:nvGrpSpPr>
+        <xdr:cNvPr id="13" name="グループ化 12">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{14EB4E5F-3205-0CBD-8D3D-2123B8EDFFA2}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGrpSpPr/>
+      </xdr:nvGrpSpPr>
+      <xdr:grpSpPr>
+        <a:xfrm>
+          <a:off x="3705225" y="1504950"/>
+          <a:ext cx="1752600" cy="2066925"/>
+          <a:chOff x="485775" y="800100"/>
+          <a:chExt cx="1752600" cy="2066925"/>
+        </a:xfrm>
+      </xdr:grpSpPr>
+      <xdr:sp macro="" textlink="">
+        <xdr:nvSpPr>
+          <xdr:cNvPr id="14" name="テキスト ボックス 13">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1A79C78D-3365-9312-DD14-198FD5CDCFBE}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvSpPr txBox="1"/>
+        </xdr:nvSpPr>
+        <xdr:spPr>
+          <a:xfrm>
+            <a:off x="523875" y="800100"/>
+            <a:ext cx="1695450" cy="304800"/>
+          </a:xfrm>
+          <a:prstGeom prst="rect">
+            <a:avLst/>
+          </a:prstGeom>
+          <a:solidFill>
+            <a:schemeClr val="accent2">
+              <a:lumMod val="40000"/>
+              <a:lumOff val="60000"/>
+            </a:schemeClr>
+          </a:solidFill>
+          <a:ln w="9525" cmpd="sng">
+            <a:solidFill>
+              <a:schemeClr val="lt1">
+                <a:shade val="50000"/>
+              </a:schemeClr>
+            </a:solidFill>
+          </a:ln>
+        </xdr:spPr>
+        <xdr:style>
+          <a:lnRef idx="0">
+            <a:scrgbClr r="0" g="0" b="0"/>
+          </a:lnRef>
+          <a:fillRef idx="0">
+            <a:scrgbClr r="0" g="0" b="0"/>
+          </a:fillRef>
+          <a:effectRef idx="0">
+            <a:scrgbClr r="0" g="0" b="0"/>
+          </a:effectRef>
+          <a:fontRef idx="minor">
+            <a:schemeClr val="dk1"/>
+          </a:fontRef>
+        </xdr:style>
+        <xdr:txBody>
+          <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="ctr"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr algn="ctr"/>
+            <a:r>
+              <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+              <a:t>センサー</a:t>
+            </a:r>
+          </a:p>
+        </xdr:txBody>
+      </xdr:sp>
+      <xdr:cxnSp macro="">
+        <xdr:nvCxnSpPr>
+          <xdr:cNvPr id="15" name="直線コネクタ 14">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0B38C314-12EB-98F6-4669-8ECBAD6D1509}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvCxnSpPr/>
+        </xdr:nvCxnSpPr>
+        <xdr:spPr>
+          <a:xfrm>
+            <a:off x="485775" y="1438275"/>
+            <a:ext cx="0" cy="1428750"/>
+          </a:xfrm>
+          <a:prstGeom prst="line">
+            <a:avLst/>
+          </a:prstGeom>
+        </xdr:spPr>
+        <xdr:style>
+          <a:lnRef idx="1">
+            <a:schemeClr val="accent1"/>
+          </a:lnRef>
+          <a:fillRef idx="0">
+            <a:schemeClr val="accent1"/>
+          </a:fillRef>
+          <a:effectRef idx="0">
+            <a:schemeClr val="accent1"/>
+          </a:effectRef>
+          <a:fontRef idx="minor">
+            <a:schemeClr val="tx1"/>
+          </a:fontRef>
+        </xdr:style>
+      </xdr:cxnSp>
+      <xdr:cxnSp macro="">
+        <xdr:nvCxnSpPr>
+          <xdr:cNvPr id="16" name="直線コネクタ 15">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B767AE60-C6FC-2080-3127-E31E86CE8004}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvCxnSpPr/>
+        </xdr:nvCxnSpPr>
+        <xdr:spPr>
+          <a:xfrm flipH="1">
+            <a:off x="485775" y="2867025"/>
+            <a:ext cx="1752600" cy="0"/>
+          </a:xfrm>
+          <a:prstGeom prst="line">
+            <a:avLst/>
+          </a:prstGeom>
+        </xdr:spPr>
+        <xdr:style>
+          <a:lnRef idx="1">
+            <a:schemeClr val="accent1"/>
+          </a:lnRef>
+          <a:fillRef idx="0">
+            <a:schemeClr val="accent1"/>
+          </a:fillRef>
+          <a:effectRef idx="0">
+            <a:schemeClr val="accent1"/>
+          </a:effectRef>
+          <a:fontRef idx="minor">
+            <a:schemeClr val="tx1"/>
+          </a:fontRef>
+        </xdr:style>
+      </xdr:cxnSp>
+      <xdr:cxnSp macro="">
+        <xdr:nvCxnSpPr>
+          <xdr:cNvPr id="17" name="直線コネクタ 16">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5DB3F6A9-DE7E-802D-A910-5DECE307314D}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvCxnSpPr/>
+        </xdr:nvCxnSpPr>
+        <xdr:spPr>
+          <a:xfrm flipV="1">
+            <a:off x="2238375" y="1447800"/>
+            <a:ext cx="0" cy="1419225"/>
+          </a:xfrm>
+          <a:prstGeom prst="line">
+            <a:avLst/>
+          </a:prstGeom>
+        </xdr:spPr>
+        <xdr:style>
+          <a:lnRef idx="1">
+            <a:schemeClr val="accent1"/>
+          </a:lnRef>
+          <a:fillRef idx="0">
+            <a:schemeClr val="accent1"/>
+          </a:fillRef>
+          <a:effectRef idx="0">
+            <a:schemeClr val="accent1"/>
+          </a:effectRef>
+          <a:fontRef idx="minor">
+            <a:schemeClr val="tx1"/>
+          </a:fontRef>
+        </xdr:style>
+      </xdr:cxnSp>
+    </xdr:grpSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>114300</xdr:colOff>
+      <xdr:row>13</xdr:row>
+      <xdr:rowOff>9525</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>17</xdr:col>
+      <xdr:colOff>57150</xdr:colOff>
+      <xdr:row>14</xdr:row>
+      <xdr:rowOff>209550</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="18" name="直方体 17">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4A08E383-EF45-B10F-CF71-6B1C8B775440}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="3581400" y="2390775"/>
+          <a:ext cx="438150" cy="438150"/>
+        </a:xfrm>
+        <a:prstGeom prst="cube">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>17</xdr:col>
+      <xdr:colOff>180975</xdr:colOff>
+      <xdr:row>12</xdr:row>
+      <xdr:rowOff>228600</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>19</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>14</xdr:row>
+      <xdr:rowOff>190500</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="19" name="直方体 18">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{CC33CF3F-1412-AC66-67D9-21D547DEAEA0}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="4143375" y="2371725"/>
+          <a:ext cx="438150" cy="438150"/>
+        </a:xfrm>
+        <a:prstGeom prst="cube">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>19</xdr:col>
+      <xdr:colOff>200025</xdr:colOff>
+      <xdr:row>12</xdr:row>
+      <xdr:rowOff>219075</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>21</xdr:col>
+      <xdr:colOff>142875</xdr:colOff>
+      <xdr:row>14</xdr:row>
+      <xdr:rowOff>180975</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="20" name="直方体 19">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D72A1274-E944-63A6-7328-AE435FFC78AA}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="4657725" y="2362200"/>
+          <a:ext cx="438150" cy="438150"/>
+        </a:xfrm>
+        <a:prstGeom prst="cube">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>19</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>11</xdr:row>
+      <xdr:rowOff>76200</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>20</xdr:col>
+      <xdr:colOff>190500</xdr:colOff>
+      <xdr:row>13</xdr:row>
+      <xdr:rowOff>38100</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="21" name="直方体 20">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{BF345900-42D7-6C17-301E-FCA79B16A4F7}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="4457700" y="1981200"/>
+          <a:ext cx="438150" cy="438150"/>
+        </a:xfrm>
+        <a:prstGeom prst="cube">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>142875</xdr:colOff>
+      <xdr:row>11</xdr:row>
+      <xdr:rowOff>85725</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>17</xdr:col>
+      <xdr:colOff>85725</xdr:colOff>
+      <xdr:row>13</xdr:row>
+      <xdr:rowOff>47625</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="22" name="直方体 21">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3225C394-8DCC-28E2-E309-6F89EB18DBD0}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="3609975" y="1990725"/>
+          <a:ext cx="438150" cy="438150"/>
+        </a:xfrm>
+        <a:prstGeom prst="cube">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>17</xdr:col>
+      <xdr:colOff>19050</xdr:colOff>
+      <xdr:row>11</xdr:row>
+      <xdr:rowOff>114300</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>18</xdr:col>
+      <xdr:colOff>209550</xdr:colOff>
+      <xdr:row>13</xdr:row>
+      <xdr:rowOff>76200</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="23" name="直方体 22">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C5B1F577-9B03-1FD8-AD0B-6221DE21C7EE}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="3981450" y="2019300"/>
+          <a:ext cx="438150" cy="438150"/>
+        </a:xfrm>
+        <a:prstGeom prst="cube">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>19</xdr:col>
+      <xdr:colOff>238125</xdr:colOff>
+      <xdr:row>9</xdr:row>
+      <xdr:rowOff>171450</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>21</xdr:col>
+      <xdr:colOff>180975</xdr:colOff>
+      <xdr:row>11</xdr:row>
+      <xdr:rowOff>133350</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="24" name="直方体 23">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C8448C4D-A682-7382-02C2-1B03ECE2CEFF}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="4695825" y="1600200"/>
+          <a:ext cx="438150" cy="438150"/>
+        </a:xfrm>
+        <a:prstGeom prst="cube">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>17</xdr:col>
+      <xdr:colOff>228600</xdr:colOff>
+      <xdr:row>9</xdr:row>
+      <xdr:rowOff>171450</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>19</xdr:col>
+      <xdr:colOff>171450</xdr:colOff>
+      <xdr:row>11</xdr:row>
+      <xdr:rowOff>133350</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="25" name="直方体 24">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{19127C41-1B61-5AED-F0AD-656869FD8343}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="4191000" y="1600200"/>
+          <a:ext cx="438150" cy="438150"/>
+        </a:xfrm>
+        <a:prstGeom prst="cube">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>180975</xdr:colOff>
+      <xdr:row>9</xdr:row>
+      <xdr:rowOff>171450</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>17</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>11</xdr:row>
+      <xdr:rowOff>133350</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="26" name="直方体 25">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{48DF7EC8-D683-486E-8986-3D15F097DD4C}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="3648075" y="1600200"/>
+          <a:ext cx="438150" cy="438150"/>
+        </a:xfrm>
+        <a:prstGeom prst="cube">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>133350</xdr:colOff>
+      <xdr:row>7</xdr:row>
+      <xdr:rowOff>171450</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>133350</xdr:colOff>
+      <xdr:row>12</xdr:row>
+      <xdr:rowOff>200025</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="28" name="直線矢印コネクタ 27">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4116BE75-5D76-ADFC-07AD-89ABD2712616}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1371600" y="1123950"/>
+          <a:ext cx="0" cy="1219200"/>
+        </a:xfrm>
+        <a:prstGeom prst="straightConnector1">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln w="22225">
+          <a:solidFill>
+            <a:srgbClr val="FF0000"/>
+          </a:solidFill>
+          <a:headEnd type="triangle"/>
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>171450</xdr:colOff>
+      <xdr:row>13</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>114300</xdr:colOff>
+      <xdr:row>14</xdr:row>
+      <xdr:rowOff>200025</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="30" name="直方体 29">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8F35DD6C-0C49-B976-D181-D4EB5193A3D1}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="666750" y="2381250"/>
+          <a:ext cx="438150" cy="438150"/>
+        </a:xfrm>
+        <a:prstGeom prst="cube">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>142875</xdr:colOff>
+      <xdr:row>13</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>85725</xdr:colOff>
+      <xdr:row>14</xdr:row>
+      <xdr:rowOff>200025</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="31" name="直方体 30">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{EA2B4599-7085-A3CC-5F53-3D2D4B569B4A}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1133475" y="2381250"/>
+          <a:ext cx="438150" cy="438150"/>
+        </a:xfrm>
+        <a:prstGeom prst="cube">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>133350</xdr:colOff>
+      <xdr:row>13</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>76200</xdr:colOff>
+      <xdr:row>14</xdr:row>
+      <xdr:rowOff>200025</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="32" name="直方体 31">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3F4C319A-B009-9503-B3C3-1694B5967D64}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1619250" y="2381250"/>
+          <a:ext cx="438150" cy="438150"/>
+        </a:xfrm>
+        <a:prstGeom prst="cube">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>18</xdr:col>
+      <xdr:colOff>200025</xdr:colOff>
+      <xdr:row>7</xdr:row>
+      <xdr:rowOff>171450</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>18</xdr:col>
+      <xdr:colOff>200025</xdr:colOff>
+      <xdr:row>9</xdr:row>
+      <xdr:rowOff>190500</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="33" name="直線矢印コネクタ 32">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7A7FCAA9-C5AB-14E8-BD95-7DCD8CF06528}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="4410075" y="1123950"/>
+          <a:ext cx="0" cy="495300"/>
+        </a:xfrm>
+        <a:prstGeom prst="straightConnector1">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln w="22225">
+          <a:solidFill>
+            <a:srgbClr val="FF0000"/>
+          </a:solidFill>
+          <a:headEnd type="triangle"/>
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>15</xdr:row>
+      <xdr:rowOff>171450</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="1877437" cy="800604"/>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="37" name="テキスト ボックス 36">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{DD6A487E-FC55-0503-ECDA-CE9819465570}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="495300" y="3028950"/>
+          <a:ext cx="1877437" cy="800604"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="none" rtlCol="0" anchor="t">
+          <a:spAutoFit/>
+        </a:bodyPr>
+        <a:lstStyle/>
+        <a:p>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+            <a:t>製品との距離が遠いため、</a:t>
+          </a:r>
+          <a:endParaRPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100"/>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100" b="1">
+              <a:solidFill>
+                <a:srgbClr val="00B050"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>「一杯になっていない」</a:t>
+          </a:r>
+          <a:endParaRPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100" b="1">
+            <a:solidFill>
+              <a:srgbClr val="00B050"/>
+            </a:solidFill>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+            <a:t>と判定</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>219075</xdr:colOff>
+      <xdr:row>15</xdr:row>
+      <xdr:rowOff>171450</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="1877437" cy="800604"/>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="38" name="テキスト ボックス 37">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E333065E-57CC-D465-97BC-1D9057C2C5B2}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="3438525" y="3028950"/>
+          <a:ext cx="1877437" cy="800604"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="none" rtlCol="0" anchor="t">
+          <a:spAutoFit/>
+        </a:bodyPr>
+        <a:lstStyle/>
+        <a:p>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+            <a:t>製品との距離が近いため、</a:t>
+          </a:r>
+          <a:endParaRPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100"/>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100" b="1">
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>「一杯になっている」</a:t>
+          </a:r>
+          <a:endParaRPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100" b="1">
+            <a:solidFill>
+              <a:srgbClr val="FF0000"/>
+            </a:solidFill>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+            <a:t>と判定</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>219075</xdr:colOff>
+      <xdr:row>23</xdr:row>
+      <xdr:rowOff>180975</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>180975</xdr:colOff>
+      <xdr:row>25</xdr:row>
+      <xdr:rowOff>9525</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="40" name="テキスト ボックス 39">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{19ADC655-4298-D190-E26F-A50088722961}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="714375" y="5648325"/>
+          <a:ext cx="1695450" cy="304800"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="accent2">
+            <a:lumMod val="40000"/>
+            <a:lumOff val="60000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:ln w="9525" cmpd="sng">
+          <a:solidFill>
+            <a:schemeClr val="lt1">
+              <a:shade val="50000"/>
+            </a:schemeClr>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="ctr"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+            <a:t>センサー</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>171450</xdr:colOff>
+      <xdr:row>27</xdr:row>
+      <xdr:rowOff>28575</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>114300</xdr:colOff>
+      <xdr:row>28</xdr:row>
+      <xdr:rowOff>228600</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="44" name="直方体 43">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B488BDBB-AE3A-4BFA-BCB8-64E2828294AC}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1409700" y="6448425"/>
+          <a:ext cx="438150" cy="438150"/>
+        </a:xfrm>
+        <a:prstGeom prst="cube">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>142875</xdr:colOff>
+      <xdr:row>25</xdr:row>
+      <xdr:rowOff>28575</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>142875</xdr:colOff>
+      <xdr:row>27</xdr:row>
+      <xdr:rowOff>47625</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="45" name="直線矢印コネクタ 44">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{FA67CADB-B986-4D27-AA24-B4352ABCD37F}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1628775" y="5972175"/>
+          <a:ext cx="0" cy="495300"/>
+        </a:xfrm>
+        <a:prstGeom prst="straightConnector1">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln w="22225">
+          <a:solidFill>
+            <a:srgbClr val="FF0000"/>
+          </a:solidFill>
+          <a:headEnd type="triangle"/>
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>35</xdr:row>
+      <xdr:rowOff>200025</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>238125</xdr:colOff>
+      <xdr:row>48</xdr:row>
+      <xdr:rowOff>66675</xdr:rowOff>
+    </xdr:to>
+    <xdr:grpSp>
+      <xdr:nvGrpSpPr>
+        <xdr:cNvPr id="54" name="グループ化 53">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E463BE2B-7671-DB0D-3F7A-9A4BBB71361B}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGrpSpPr/>
+      </xdr:nvGrpSpPr>
+      <xdr:grpSpPr>
+        <a:xfrm>
+          <a:off x="742950" y="8524875"/>
+          <a:ext cx="2962275" cy="2962275"/>
+          <a:chOff x="742950" y="8524875"/>
+          <a:chExt cx="2962275" cy="2962275"/>
+        </a:xfrm>
+      </xdr:grpSpPr>
+      <xdr:grpSp>
+        <xdr:nvGrpSpPr>
+          <xdr:cNvPr id="50" name="グループ化 49">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D3563E00-61EA-03B8-698C-1BC4AAD018AF}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvGrpSpPr/>
+        </xdr:nvGrpSpPr>
+        <xdr:grpSpPr>
+          <a:xfrm>
+            <a:off x="742950" y="8524875"/>
+            <a:ext cx="2962275" cy="2962275"/>
+            <a:chOff x="742950" y="8524875"/>
+            <a:chExt cx="2962275" cy="2962275"/>
+          </a:xfrm>
+        </xdr:grpSpPr>
+        <xdr:pic>
+          <xdr:nvPicPr>
+            <xdr:cNvPr id="46" name="図 45">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4A84649F-F4AC-BD29-3CC6-F78B61D1D9C1}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvPicPr>
+              <a:picLocks noChangeAspect="1"/>
+            </xdr:cNvPicPr>
+          </xdr:nvPicPr>
+          <xdr:blipFill>
+            <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+            <a:stretch>
+              <a:fillRect/>
+            </a:stretch>
+          </xdr:blipFill>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="742950" y="8524875"/>
+              <a:ext cx="2962275" cy="2962275"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+          </xdr:spPr>
+        </xdr:pic>
+        <xdr:pic>
+          <xdr:nvPicPr>
+            <xdr:cNvPr id="49" name="図 48">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9F6BF160-F74E-7458-8869-A0E2BF40B97E}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvPicPr>
+              <a:picLocks noChangeAspect="1"/>
+            </xdr:cNvPicPr>
+          </xdr:nvPicPr>
+          <xdr:blipFill>
+            <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+            <a:stretch>
+              <a:fillRect/>
+            </a:stretch>
+          </xdr:blipFill>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="1514475" y="10058400"/>
+              <a:ext cx="1619250" cy="238158"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+          </xdr:spPr>
+        </xdr:pic>
+      </xdr:grpSp>
+      <xdr:sp macro="" textlink="">
+        <xdr:nvSpPr>
+          <xdr:cNvPr id="51" name="テキスト ボックス 50">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{243B9637-123B-9F64-A902-30433AC3A2DE}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvSpPr txBox="1"/>
+        </xdr:nvSpPr>
+        <xdr:spPr>
+          <a:xfrm>
+            <a:off x="1257300" y="9258300"/>
+            <a:ext cx="2080570" cy="1469954"/>
+          </a:xfrm>
+          <a:prstGeom prst="rect">
+            <a:avLst/>
+          </a:prstGeom>
+          <a:noFill/>
+        </xdr:spPr>
+        <xdr:style>
+          <a:lnRef idx="0">
+            <a:scrgbClr r="0" g="0" b="0"/>
+          </a:lnRef>
+          <a:fillRef idx="0">
+            <a:scrgbClr r="0" g="0" b="0"/>
+          </a:fillRef>
+          <a:effectRef idx="0">
+            <a:scrgbClr r="0" g="0" b="0"/>
+          </a:effectRef>
+          <a:fontRef idx="minor">
+            <a:schemeClr val="tx1"/>
+          </a:fontRef>
+        </xdr:style>
+        <xdr:txBody>
+          <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="none" rtlCol="0" anchor="t">
+            <a:spAutoFit/>
+          </a:bodyPr>
+          <a:lstStyle/>
+          <a:p>
+            <a:r>
+              <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="8800"/>
+              <a:t>30</a:t>
+            </a:r>
+            <a:r>
+              <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="4800"/>
+              <a:t>cm</a:t>
+            </a:r>
+            <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="8800"/>
+          </a:p>
+        </xdr:txBody>
+      </xdr:sp>
+    </xdr:grpSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>76200</xdr:colOff>
+      <xdr:row>35</xdr:row>
+      <xdr:rowOff>200025</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>28</xdr:col>
+      <xdr:colOff>66675</xdr:colOff>
+      <xdr:row>48</xdr:row>
+      <xdr:rowOff>66675</xdr:rowOff>
+    </xdr:to>
+    <xdr:grpSp>
+      <xdr:nvGrpSpPr>
+        <xdr:cNvPr id="53" name="グループ化 52">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{08488AEF-7A3A-A4A6-56DD-0184BBF7B6B7}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGrpSpPr/>
+      </xdr:nvGrpSpPr>
+      <xdr:grpSpPr>
+        <a:xfrm>
+          <a:off x="4038600" y="8524875"/>
+          <a:ext cx="2962275" cy="2962275"/>
+          <a:chOff x="4038600" y="8524875"/>
+          <a:chExt cx="2962275" cy="2962275"/>
+        </a:xfrm>
+      </xdr:grpSpPr>
+      <xdr:pic>
+        <xdr:nvPicPr>
+          <xdr:cNvPr id="47" name="図 46">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{BFC5ED8D-46F4-9457-2DFF-29BE2B9FE259}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvPicPr>
+            <a:picLocks noChangeAspect="1"/>
+          </xdr:cNvPicPr>
+        </xdr:nvPicPr>
+        <xdr:blipFill>
+          <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+          <a:stretch>
+            <a:fillRect/>
+          </a:stretch>
+        </xdr:blipFill>
+        <xdr:spPr>
+          <a:xfrm>
+            <a:off x="4038600" y="8524875"/>
+            <a:ext cx="2962275" cy="2962275"/>
+          </a:xfrm>
+          <a:prstGeom prst="rect">
+            <a:avLst/>
+          </a:prstGeom>
+        </xdr:spPr>
+      </xdr:pic>
+      <xdr:sp macro="" textlink="">
+        <xdr:nvSpPr>
+          <xdr:cNvPr id="48" name="正方形/長方形 47">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{58B50D33-6551-8F57-065F-CA0DFB702A98}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvSpPr/>
+        </xdr:nvSpPr>
+        <xdr:spPr>
+          <a:xfrm>
+            <a:off x="4162424" y="8877300"/>
+            <a:ext cx="2809875" cy="2114550"/>
+          </a:xfrm>
+          <a:prstGeom prst="rect">
+            <a:avLst/>
+          </a:prstGeom>
+          <a:solidFill>
+            <a:srgbClr val="FF0000"/>
+          </a:solidFill>
+        </xdr:spPr>
+        <xdr:style>
+          <a:lnRef idx="2">
+            <a:schemeClr val="accent1">
+              <a:shade val="15000"/>
+            </a:schemeClr>
+          </a:lnRef>
+          <a:fillRef idx="1">
+            <a:schemeClr val="accent1"/>
+          </a:fillRef>
+          <a:effectRef idx="0">
+            <a:schemeClr val="accent1"/>
+          </a:effectRef>
+          <a:fontRef idx="minor">
+            <a:schemeClr val="lt1"/>
+          </a:fontRef>
+        </xdr:style>
+        <xdr:txBody>
+          <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr algn="l"/>
+            <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+          </a:p>
+        </xdr:txBody>
+      </xdr:sp>
+      <xdr:sp macro="" textlink="">
+        <xdr:nvSpPr>
+          <xdr:cNvPr id="52" name="テキスト ボックス 51">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3376D57B-8396-8492-DBFE-59286CD2C26F}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvSpPr txBox="1"/>
+        </xdr:nvSpPr>
+        <xdr:spPr>
+          <a:xfrm>
+            <a:off x="4600575" y="9210675"/>
+            <a:ext cx="2080570" cy="1469954"/>
+          </a:xfrm>
+          <a:prstGeom prst="rect">
+            <a:avLst/>
+          </a:prstGeom>
+          <a:noFill/>
+        </xdr:spPr>
+        <xdr:style>
+          <a:lnRef idx="0">
+            <a:scrgbClr r="0" g="0" b="0"/>
+          </a:lnRef>
+          <a:fillRef idx="0">
+            <a:scrgbClr r="0" g="0" b="0"/>
+          </a:fillRef>
+          <a:effectRef idx="0">
+            <a:scrgbClr r="0" g="0" b="0"/>
+          </a:effectRef>
+          <a:fontRef idx="minor">
+            <a:schemeClr val="tx1"/>
+          </a:fontRef>
+        </xdr:style>
+        <xdr:txBody>
+          <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="none" rtlCol="0" anchor="t">
+            <a:spAutoFit/>
+          </a:bodyPr>
+          <a:lstStyle/>
+          <a:p>
+            <a:r>
+              <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="8800"/>
+              <a:t>10</a:t>
+            </a:r>
+            <a:r>
+              <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="4800"/>
+              <a:t>cm</a:t>
+            </a:r>
+            <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="8800"/>
+          </a:p>
+        </xdr:txBody>
+      </xdr:sp>
+    </xdr:grpSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -569,15 +2961,6 @@
     <row r="6" spans="2:18">
       <c r="F6" s="1"/>
       <c r="H6" s="8"/>
-      <c r="I6" s="9"/>
-      <c r="J6" s="9"/>
-      <c r="K6" s="9"/>
-      <c r="L6" s="9"/>
-      <c r="M6" s="9"/>
-      <c r="N6" s="9"/>
-      <c r="O6" s="9"/>
-      <c r="P6" s="9"/>
-      <c r="Q6" s="9"/>
       <c r="R6" s="1"/>
     </row>
     <row r="7" spans="2:18">
@@ -598,15 +2981,9 @@
       <c r="F8" s="1"/>
       <c r="H8" s="8"/>
       <c r="I8" s="8"/>
-      <c r="J8" s="9"/>
-      <c r="K8" s="9"/>
-      <c r="L8" s="9" t="s">
+      <c r="L8" t="s">
         <v>4</v>
       </c>
-      <c r="M8" s="9"/>
-      <c r="N8" s="9"/>
-      <c r="O8" s="9"/>
-      <c r="P8" s="9"/>
       <c r="Q8" s="1"/>
       <c r="R8" s="1"/>
     </row>
@@ -614,42 +2991,26 @@
       <c r="F9" s="1"/>
       <c r="H9" s="8"/>
       <c r="I9" s="8"/>
-      <c r="J9" s="9"/>
-      <c r="K9" s="9"/>
-      <c r="L9" s="9"/>
-      <c r="M9" s="9"/>
-      <c r="N9" s="9"/>
-      <c r="O9" s="9"/>
-      <c r="P9" s="9"/>
       <c r="Q9" s="1"/>
       <c r="R9" s="1"/>
     </row>
     <row r="10" spans="2:18">
       <c r="F10" s="1"/>
       <c r="H10" s="8"/>
-      <c r="I10" s="10"/>
-      <c r="J10" s="11"/>
-      <c r="K10" s="11"/>
-      <c r="L10" s="11"/>
-      <c r="M10" s="11"/>
-      <c r="N10" s="11"/>
-      <c r="O10" s="11"/>
-      <c r="P10" s="11"/>
-      <c r="Q10" s="12"/>
+      <c r="I10" s="9"/>
+      <c r="J10" s="10"/>
+      <c r="K10" s="10"/>
+      <c r="L10" s="10"/>
+      <c r="M10" s="10"/>
+      <c r="N10" s="10"/>
+      <c r="O10" s="10"/>
+      <c r="P10" s="10"/>
+      <c r="Q10" s="11"/>
       <c r="R10" s="1"/>
     </row>
     <row r="11" spans="2:18">
       <c r="F11" s="1"/>
       <c r="H11" s="8"/>
-      <c r="I11" s="9"/>
-      <c r="J11" s="9"/>
-      <c r="K11" s="9"/>
-      <c r="L11" s="9"/>
-      <c r="M11" s="9"/>
-      <c r="N11" s="9"/>
-      <c r="O11" s="9"/>
-      <c r="P11" s="9"/>
-      <c r="Q11" s="9"/>
       <c r="R11" s="1"/>
     </row>
     <row r="12" spans="2:18">
@@ -675,7 +3036,6 @@
       </c>
       <c r="K13" s="3"/>
       <c r="L13" s="4"/>
-      <c r="M13" s="9"/>
       <c r="N13" s="2" t="s">
         <v>6</v>
       </c>
@@ -687,30 +3047,30 @@
     <row r="14" spans="2:18">
       <c r="F14" s="1"/>
       <c r="H14" s="8"/>
-      <c r="I14" s="10"/>
-      <c r="J14" s="11"/>
-      <c r="K14" s="11"/>
-      <c r="L14" s="11"/>
-      <c r="M14" s="11"/>
-      <c r="N14" s="11"/>
-      <c r="O14" s="11"/>
-      <c r="P14" s="11"/>
-      <c r="Q14" s="12"/>
+      <c r="I14" s="9"/>
+      <c r="J14" s="10"/>
+      <c r="K14" s="10"/>
+      <c r="L14" s="10"/>
+      <c r="M14" s="10"/>
+      <c r="N14" s="10"/>
+      <c r="O14" s="10"/>
+      <c r="P14" s="10"/>
+      <c r="Q14" s="11"/>
       <c r="R14" s="1"/>
     </row>
     <row r="15" spans="2:18">
       <c r="F15" s="1"/>
-      <c r="H15" s="10"/>
-      <c r="I15" s="11"/>
-      <c r="J15" s="11"/>
-      <c r="K15" s="11"/>
-      <c r="L15" s="11"/>
-      <c r="M15" s="11"/>
-      <c r="N15" s="11"/>
-      <c r="O15" s="11"/>
-      <c r="P15" s="11"/>
-      <c r="Q15" s="11"/>
-      <c r="R15" s="12"/>
+      <c r="H15" s="9"/>
+      <c r="I15" s="10"/>
+      <c r="J15" s="10"/>
+      <c r="K15" s="10"/>
+      <c r="L15" s="10"/>
+      <c r="M15" s="10"/>
+      <c r="N15" s="10"/>
+      <c r="O15" s="10"/>
+      <c r="P15" s="10"/>
+      <c r="Q15" s="10"/>
+      <c r="R15" s="11"/>
     </row>
     <row r="16" spans="2:18">
       <c r="F16" s="1"/>
@@ -746,4 +3106,259 @@
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{65C45921-06FE-4B81-BC0C-E57414EB5CD4}">
+  <dimension ref="A1:Q93"/>
+  <sheetFormatPr defaultColWidth="3.25" defaultRowHeight="18.75"/>
+  <sheetData>
+    <row r="1" spans="1:3" s="12" customFormat="1" ht="18">
+      <c r="A1" s="12" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3">
+      <c r="B3" s="13" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3">
+      <c r="C5" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="21" spans="2:13">
+      <c r="B21" s="13" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="23" spans="2:13">
+      <c r="C23" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="25" spans="2:13">
+      <c r="M25" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="31" spans="2:13">
+      <c r="B31" s="13" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="33" spans="3:17">
+      <c r="C33" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="35" spans="3:17">
+      <c r="D35" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q35" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="51" spans="1:10">
+      <c r="C51" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="53" spans="1:10" s="12" customFormat="1" ht="18">
+      <c r="A53" s="12" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="55" spans="1:10">
+      <c r="B55" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="57" spans="1:10">
+      <c r="C57" s="14" t="s">
+        <v>21</v>
+      </c>
+      <c r="D57" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="59" spans="1:10">
+      <c r="D59" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="60" spans="1:10">
+      <c r="D60" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="61" spans="1:10">
+      <c r="E61" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="62" spans="1:10">
+      <c r="F62" t="s">
+        <v>24</v>
+      </c>
+      <c r="J62" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="63" spans="1:10">
+      <c r="F63" t="s">
+        <v>25</v>
+      </c>
+      <c r="J63" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="64" spans="1:10">
+      <c r="F64" t="s">
+        <v>38</v>
+      </c>
+      <c r="J64" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="65" spans="2:5">
+      <c r="E65" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="67" spans="2:5">
+      <c r="B67" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="69" spans="2:5">
+      <c r="C69" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="71" spans="2:5">
+      <c r="D71" t="s">
+        <v>36</v>
+      </c>
+      <c r="E71" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="73" spans="2:5">
+      <c r="E73" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="74" spans="2:5">
+      <c r="E74" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="75" spans="2:5">
+      <c r="E75" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="76" spans="2:5">
+      <c r="E76" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="78" spans="2:5">
+      <c r="D78" t="s">
+        <v>35</v>
+      </c>
+      <c r="E78" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="80" spans="2:5">
+      <c r="E80" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="81" spans="4:17">
+      <c r="E81" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="83" spans="4:17">
+      <c r="D83" t="s">
+        <v>44</v>
+      </c>
+      <c r="E83" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="85" spans="4:17">
+      <c r="E85" t="s">
+        <v>47</v>
+      </c>
+      <c r="O85" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="87" spans="4:17">
+      <c r="F87" t="s">
+        <v>23</v>
+      </c>
+      <c r="P87" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="88" spans="4:17">
+      <c r="F88" t="s">
+        <v>27</v>
+      </c>
+      <c r="P88" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="89" spans="4:17">
+      <c r="G89" t="s">
+        <v>49</v>
+      </c>
+      <c r="Q89" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="90" spans="4:17">
+      <c r="G90" t="s">
+        <v>45</v>
+      </c>
+      <c r="Q90" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="91" spans="4:17">
+      <c r="G91" t="s">
+        <v>51</v>
+      </c>
+      <c r="Q91" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="92" spans="4:17">
+      <c r="G92" t="s">
+        <v>50</v>
+      </c>
+      <c r="Q92" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="93" spans="4:17">
+      <c r="F93" t="s">
+        <v>26</v>
+      </c>
+      <c r="P93" t="s">
+        <v>26</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
 </file>
--- a/設計書.xlsx
+++ b/設計書.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\ikura\次世代開発\ソース\CounterServer\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BF3EE5A8-155F-47F8-B442-9FFEBDCA63E3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{35D7A7B2-A6AC-440B-8A67-400FD2427ED6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="レイアウト" sheetId="1" r:id="rId1"/>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="63" uniqueCount="53">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="155" uniqueCount="91">
   <si>
     <t>Home</t>
     <phoneticPr fontId="1"/>
@@ -339,9 +339,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>DBへ保存</t>
-  </si>
-  <si>
     <t>no</t>
     <phoneticPr fontId="1"/>
   </si>
@@ -448,25 +445,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>算出時間に応じて通知を送信する</t>
-    <rPh sb="0" eb="2">
-      <t>サンシュツ</t>
-    </rPh>
-    <rPh sb="2" eb="4">
-      <t>ジカン</t>
-    </rPh>
-    <rPh sb="5" eb="6">
-      <t>オウ</t>
-    </rPh>
-    <rPh sb="8" eb="10">
-      <t>ツウチ</t>
-    </rPh>
-    <rPh sb="11" eb="13">
-      <t>ソウシン</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>指定秒以上の場合</t>
     <rPh sb="0" eb="3">
       <t>シテイビョウ</t>
@@ -493,25 +471,413 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>type : "lenge"</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>lenge : 最新の距離</t>
+    <t>alert : "full"</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>alert : ""</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>※何秒に１回センサーで読み取るかの秒を使う</t>
+    <rPh sb="1" eb="3">
+      <t>ナンビョウ</t>
+    </rPh>
+    <rPh sb="5" eb="6">
+      <t>カイ</t>
+    </rPh>
+    <rPh sb="11" eb="12">
+      <t>ヨ</t>
+    </rPh>
+    <rPh sb="13" eb="14">
+      <t>ト</t>
+    </rPh>
+    <rPh sb="17" eb="18">
+      <t>ビョウ</t>
+    </rPh>
+    <rPh sb="19" eb="20">
+      <t>ツカ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>算出時間に応じて通知を送信する。</t>
+    <rPh sb="0" eb="2">
+      <t>サンシュツ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>ジカン</t>
+    </rPh>
+    <rPh sb="5" eb="6">
+      <t>オウ</t>
+    </rPh>
     <rPh sb="8" eb="10">
+      <t>ツウチ</t>
+    </rPh>
+    <rPh sb="11" eb="13">
+      <t>ソウシン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>設定を受け取った時</t>
+    <rPh sb="0" eb="2">
+      <t>セッテイ</t>
+    </rPh>
+    <rPh sb="3" eb="4">
+      <t>ウ</t>
+    </rPh>
+    <rPh sb="5" eb="6">
+      <t>ト</t>
+    </rPh>
+    <rPh sb="8" eb="9">
+      <t>トキ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>DBへ保存</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>distance</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>distancements</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>distanceenv</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Fullの距離</t>
+    <rPh sb="5" eb="7">
+      <t>キョリ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>計測秒</t>
+    <rPh sb="0" eb="2">
+      <t>ケイソク</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>ビョウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>受信した設定内容を保存する</t>
+    <rPh sb="0" eb="2">
+      <t>ジュシン</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>セッテイ</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>ナイヨウ</t>
+    </rPh>
+    <rPh sb="9" eb="11">
+      <t>ホゾン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>設定取得を受け取った時</t>
+    <rPh sb="0" eb="2">
+      <t>セッテイ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>シュトク</t>
+    </rPh>
+    <rPh sb="5" eb="6">
+      <t>ウ</t>
+    </rPh>
+    <rPh sb="7" eb="8">
+      <t>ト</t>
+    </rPh>
+    <rPh sb="10" eb="11">
+      <t>トキ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>distanceenvから設定を読み込み、JSONで返す</t>
+    <rPh sb="13" eb="15">
+      <t>セッテイ</t>
+    </rPh>
+    <rPh sb="16" eb="17">
+      <t>ヨ</t>
+    </rPh>
+    <rPh sb="18" eb="19">
+      <t>コ</t>
+    </rPh>
+    <rPh sb="26" eb="27">
+      <t>カエ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>distance : Fullの距離</t>
+    <rPh sb="16" eb="18">
+      <t>キョリ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>sec : 計測秒</t>
+    <rPh sb="6" eb="9">
+      <t>ケイソクビョウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>type : "setenv"</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>distanceenvでレコードがない場合は、.envで設定された初期値を返す。</t>
+    <rPh sb="19" eb="21">
+      <t>バアイ</t>
+    </rPh>
+    <rPh sb="28" eb="30">
+      <t>セッテイ</t>
+    </rPh>
+    <rPh sb="33" eb="36">
+      <t>ショキチ</t>
+    </rPh>
+    <rPh sb="37" eb="38">
+      <t>カエ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>.env</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>INIT_DIST</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>INIT_SEC</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>計測秒</t>
+    <rPh sb="0" eb="3">
+      <t>ケイソクビョウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>取得元からのJSON</t>
+    <rPh sb="0" eb="2">
+      <t>シュトク</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>モト</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>type : "getenv"</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>webサーバの動作</t>
+    <rPh sb="7" eb="9">
+      <t>ドウサ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>距離情報の取得を受け取った時</t>
+    <rPh sb="0" eb="4">
+      <t>キョリジョウホウ</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>シュトク</t>
+    </rPh>
+    <rPh sb="8" eb="9">
+      <t>ウ</t>
+    </rPh>
+    <rPh sb="10" eb="11">
+      <t>ト</t>
+    </rPh>
+    <rPh sb="13" eb="14">
+      <t>トキ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>取得元からのJSON</t>
+    <rPh sb="0" eb="3">
+      <t>シュトクモト</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>type : "distance"</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>type : "getdistance"</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>サーバからの戻り値</t>
+    <rPh sb="6" eb="7">
+      <t>モド</t>
+    </rPh>
+    <rPh sb="8" eb="9">
+      <t>アタイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>※距離情報を受け取った時に返ってくる内容と同じ</t>
+    <rPh sb="1" eb="5">
+      <t>キョリジョウホウ</t>
+    </rPh>
+    <rPh sb="6" eb="7">
+      <t>ウ</t>
+    </rPh>
+    <rPh sb="8" eb="9">
+      <t>ト</t>
+    </rPh>
+    <rPh sb="11" eb="12">
+      <t>トキ</t>
+    </rPh>
+    <rPh sb="13" eb="14">
+      <t>カエ</t>
+    </rPh>
+    <rPh sb="18" eb="20">
+      <t>ナイヨウ</t>
+    </rPh>
+    <rPh sb="21" eb="22">
+      <t>オナ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>取得JSON</t>
+    <rPh sb="0" eb="2">
+      <t>シュトク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>alert : full or 空白</t>
+    <rPh sb="16" eb="18">
+      <t>クウハク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>距離を取得した時のalertに応じた動作</t>
+    <rPh sb="0" eb="2">
+      <t>キョリ</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>シュトク</t>
+    </rPh>
+    <rPh sb="7" eb="8">
+      <t>トキ</t>
+    </rPh>
+    <rPh sb="15" eb="16">
+      <t>オウ</t>
+    </rPh>
+    <rPh sb="18" eb="20">
+      <t>ドウサ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>alertが "空白" の場合</t>
+    <rPh sb="8" eb="10">
+      <t>クウハク</t>
+    </rPh>
+    <rPh sb="13" eb="15">
+      <t>バアイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>alertが "full" の場合</t>
+    <rPh sb="15" eb="17">
+      <t>バアイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>距離更新時（Updateボタンクリック時）</t>
+    <rPh sb="0" eb="2">
+      <t>キョリ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>コウシン</t>
+    </rPh>
+    <rPh sb="4" eb="5">
+      <t>ジ</t>
+    </rPh>
+    <rPh sb="19" eb="20">
+      <t>ジ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>距離と時間の設定ボタンをクリックした時</t>
+    <rPh sb="0" eb="2">
+      <t>キョリ</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>ジカン</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>セッテイ</t>
+    </rPh>
+    <rPh sb="18" eb="19">
+      <t>トキ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>type : "dist"</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>dist : 最新の距離</t>
+    <rPh sb="7" eb="9">
       <t>サイシン</t>
     </rPh>
-    <rPh sb="11" eb="13">
+    <rPh sb="10" eb="12">
       <t>キョリ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>alert : "full"</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>alert : ""</t>
+    <t>受信JSON</t>
+    <rPh sb="0" eb="2">
+      <t>ジュシン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>dist : Fullの距離</t>
+    <rPh sb="12" eb="14">
+      <t>キョリ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>type</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>"distenv"</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -702,7 +1068,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
   </cellXfs>
@@ -2638,6 +3004,961 @@
     </xdr:grpSp>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>176</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>238125</xdr:colOff>
+      <xdr:row>188</xdr:row>
+      <xdr:rowOff>104775</xdr:rowOff>
+    </xdr:to>
+    <xdr:grpSp>
+      <xdr:nvGrpSpPr>
+        <xdr:cNvPr id="55" name="グループ化 54">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{51C41088-909F-44B1-8557-42A701CC6A31}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGrpSpPr/>
+      </xdr:nvGrpSpPr>
+      <xdr:grpSpPr>
+        <a:xfrm>
+          <a:off x="990600" y="41890950"/>
+          <a:ext cx="2962275" cy="2962275"/>
+          <a:chOff x="742950" y="8524875"/>
+          <a:chExt cx="2962275" cy="2962275"/>
+        </a:xfrm>
+      </xdr:grpSpPr>
+      <xdr:grpSp>
+        <xdr:nvGrpSpPr>
+          <xdr:cNvPr id="56" name="グループ化 55">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4C6D655D-498E-6DF2-5503-2A6065E13F6F}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvGrpSpPr/>
+        </xdr:nvGrpSpPr>
+        <xdr:grpSpPr>
+          <a:xfrm>
+            <a:off x="742950" y="8524875"/>
+            <a:ext cx="2962275" cy="2962275"/>
+            <a:chOff x="742950" y="8524875"/>
+            <a:chExt cx="2962275" cy="2962275"/>
+          </a:xfrm>
+        </xdr:grpSpPr>
+        <xdr:pic>
+          <xdr:nvPicPr>
+            <xdr:cNvPr id="58" name="図 57">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3612715A-7537-EE37-9926-0DDB9E77EAC3}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvPicPr>
+              <a:picLocks noChangeAspect="1"/>
+            </xdr:cNvPicPr>
+          </xdr:nvPicPr>
+          <xdr:blipFill>
+            <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+            <a:stretch>
+              <a:fillRect/>
+            </a:stretch>
+          </xdr:blipFill>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="742950" y="8524875"/>
+              <a:ext cx="2962275" cy="2962275"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+          </xdr:spPr>
+        </xdr:pic>
+        <xdr:pic>
+          <xdr:nvPicPr>
+            <xdr:cNvPr id="59" name="図 58">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{821D0AB4-4E3A-3F6F-ED99-BD25B601C3B2}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvPicPr>
+              <a:picLocks noChangeAspect="1"/>
+            </xdr:cNvPicPr>
+          </xdr:nvPicPr>
+          <xdr:blipFill>
+            <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+            <a:stretch>
+              <a:fillRect/>
+            </a:stretch>
+          </xdr:blipFill>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="1514475" y="10058400"/>
+              <a:ext cx="1619250" cy="238158"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+          </xdr:spPr>
+        </xdr:pic>
+      </xdr:grpSp>
+      <xdr:sp macro="" textlink="">
+        <xdr:nvSpPr>
+          <xdr:cNvPr id="57" name="テキスト ボックス 56">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{823D9BE6-C7B2-9B2F-8190-BD80A9E17846}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvSpPr txBox="1"/>
+        </xdr:nvSpPr>
+        <xdr:spPr>
+          <a:xfrm>
+            <a:off x="1257300" y="9258300"/>
+            <a:ext cx="2080570" cy="1469954"/>
+          </a:xfrm>
+          <a:prstGeom prst="rect">
+            <a:avLst/>
+          </a:prstGeom>
+          <a:noFill/>
+        </xdr:spPr>
+        <xdr:style>
+          <a:lnRef idx="0">
+            <a:scrgbClr r="0" g="0" b="0"/>
+          </a:lnRef>
+          <a:fillRef idx="0">
+            <a:scrgbClr r="0" g="0" b="0"/>
+          </a:fillRef>
+          <a:effectRef idx="0">
+            <a:scrgbClr r="0" g="0" b="0"/>
+          </a:effectRef>
+          <a:fontRef idx="minor">
+            <a:schemeClr val="tx1"/>
+          </a:fontRef>
+        </xdr:style>
+        <xdr:txBody>
+          <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="none" rtlCol="0" anchor="t">
+            <a:spAutoFit/>
+          </a:bodyPr>
+          <a:lstStyle/>
+          <a:p>
+            <a:r>
+              <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="8800"/>
+              <a:t>30</a:t>
+            </a:r>
+            <a:r>
+              <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="4800"/>
+              <a:t>cm</a:t>
+            </a:r>
+            <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="8800"/>
+          </a:p>
+        </xdr:txBody>
+      </xdr:sp>
+    </xdr:grpSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>19</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>176</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>30</xdr:col>
+      <xdr:colOff>238125</xdr:colOff>
+      <xdr:row>188</xdr:row>
+      <xdr:rowOff>104775</xdr:rowOff>
+    </xdr:to>
+    <xdr:grpSp>
+      <xdr:nvGrpSpPr>
+        <xdr:cNvPr id="60" name="グループ化 59">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{73E2FF4F-65B1-4835-853F-69A1B8E33D57}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGrpSpPr/>
+      </xdr:nvGrpSpPr>
+      <xdr:grpSpPr>
+        <a:xfrm>
+          <a:off x="4705350" y="41890950"/>
+          <a:ext cx="2962275" cy="2962275"/>
+          <a:chOff x="4038600" y="8524875"/>
+          <a:chExt cx="2962275" cy="2962275"/>
+        </a:xfrm>
+      </xdr:grpSpPr>
+      <xdr:pic>
+        <xdr:nvPicPr>
+          <xdr:cNvPr id="61" name="図 60">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6C26663E-9316-A5CD-414D-354F06642BF6}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvPicPr>
+            <a:picLocks noChangeAspect="1"/>
+          </xdr:cNvPicPr>
+        </xdr:nvPicPr>
+        <xdr:blipFill>
+          <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+          <a:stretch>
+            <a:fillRect/>
+          </a:stretch>
+        </xdr:blipFill>
+        <xdr:spPr>
+          <a:xfrm>
+            <a:off x="4038600" y="8524875"/>
+            <a:ext cx="2962275" cy="2962275"/>
+          </a:xfrm>
+          <a:prstGeom prst="rect">
+            <a:avLst/>
+          </a:prstGeom>
+        </xdr:spPr>
+      </xdr:pic>
+      <xdr:sp macro="" textlink="">
+        <xdr:nvSpPr>
+          <xdr:cNvPr id="62" name="正方形/長方形 61">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1B2B619C-9CC6-C29E-6B80-AB7B25AB8B31}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvSpPr/>
+        </xdr:nvSpPr>
+        <xdr:spPr>
+          <a:xfrm>
+            <a:off x="4162424" y="8877300"/>
+            <a:ext cx="2809875" cy="2114550"/>
+          </a:xfrm>
+          <a:prstGeom prst="rect">
+            <a:avLst/>
+          </a:prstGeom>
+          <a:solidFill>
+            <a:srgbClr val="FF0000"/>
+          </a:solidFill>
+        </xdr:spPr>
+        <xdr:style>
+          <a:lnRef idx="2">
+            <a:schemeClr val="accent1">
+              <a:shade val="15000"/>
+            </a:schemeClr>
+          </a:lnRef>
+          <a:fillRef idx="1">
+            <a:schemeClr val="accent1"/>
+          </a:fillRef>
+          <a:effectRef idx="0">
+            <a:schemeClr val="accent1"/>
+          </a:effectRef>
+          <a:fontRef idx="minor">
+            <a:schemeClr val="lt1"/>
+          </a:fontRef>
+        </xdr:style>
+        <xdr:txBody>
+          <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr algn="l"/>
+            <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+          </a:p>
+        </xdr:txBody>
+      </xdr:sp>
+      <xdr:sp macro="" textlink="">
+        <xdr:nvSpPr>
+          <xdr:cNvPr id="63" name="テキスト ボックス 62">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2F37524E-AB2A-67BE-79E1-2848590FA57C}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvSpPr txBox="1"/>
+        </xdr:nvSpPr>
+        <xdr:spPr>
+          <a:xfrm>
+            <a:off x="4600575" y="9210675"/>
+            <a:ext cx="2080570" cy="1469954"/>
+          </a:xfrm>
+          <a:prstGeom prst="rect">
+            <a:avLst/>
+          </a:prstGeom>
+          <a:noFill/>
+        </xdr:spPr>
+        <xdr:style>
+          <a:lnRef idx="0">
+            <a:scrgbClr r="0" g="0" b="0"/>
+          </a:lnRef>
+          <a:fillRef idx="0">
+            <a:scrgbClr r="0" g="0" b="0"/>
+          </a:fillRef>
+          <a:effectRef idx="0">
+            <a:scrgbClr r="0" g="0" b="0"/>
+          </a:effectRef>
+          <a:fontRef idx="minor">
+            <a:schemeClr val="tx1"/>
+          </a:fontRef>
+        </xdr:style>
+        <xdr:txBody>
+          <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="none" rtlCol="0" anchor="t">
+            <a:spAutoFit/>
+          </a:bodyPr>
+          <a:lstStyle/>
+          <a:p>
+            <a:r>
+              <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="8800"/>
+              <a:t>10</a:t>
+            </a:r>
+            <a:r>
+              <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="4800"/>
+              <a:t>cm</a:t>
+            </a:r>
+            <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="8800"/>
+          </a:p>
+        </xdr:txBody>
+      </xdr:sp>
+    </xdr:grpSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>19050</xdr:colOff>
+      <xdr:row>186</xdr:row>
+      <xdr:rowOff>104775</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>180975</xdr:colOff>
+      <xdr:row>188</xdr:row>
+      <xdr:rowOff>95250</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="65" name="直線コネクタ 64">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F84204F3-1795-4BCF-8927-49EAFE0A4EB2}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm flipV="1">
+          <a:off x="1752600" y="41995725"/>
+          <a:ext cx="657225" cy="466725"/>
+        </a:xfrm>
+        <a:prstGeom prst="line">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln w="34925">
+          <a:solidFill>
+            <a:srgbClr val="FF0000"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>22</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>186</xdr:row>
+      <xdr:rowOff>104775</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>24</xdr:col>
+      <xdr:colOff>161925</xdr:colOff>
+      <xdr:row>188</xdr:row>
+      <xdr:rowOff>95250</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="66" name="直線コネクタ 65">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7942673B-ABE2-EE0C-97A7-0EE25FF1EAF3}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm flipV="1">
+          <a:off x="5448300" y="41995725"/>
+          <a:ext cx="657225" cy="466725"/>
+        </a:xfrm>
+        <a:prstGeom prst="line">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln w="34925">
+          <a:solidFill>
+            <a:srgbClr val="FF0000"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>228600</xdr:colOff>
+      <xdr:row>191</xdr:row>
+      <xdr:rowOff>133350</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>28575</xdr:colOff>
+      <xdr:row>206</xdr:row>
+      <xdr:rowOff>9525</xdr:rowOff>
+    </xdr:to>
+    <xdr:grpSp>
+      <xdr:nvGrpSpPr>
+        <xdr:cNvPr id="79" name="グループ化 78">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{CA13E83E-8BFF-C1CE-106A-EFCA17B167F6}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGrpSpPr/>
+      </xdr:nvGrpSpPr>
+      <xdr:grpSpPr>
+        <a:xfrm>
+          <a:off x="971550" y="45596175"/>
+          <a:ext cx="3019425" cy="3448050"/>
+          <a:chOff x="971550" y="43214925"/>
+          <a:chExt cx="3019425" cy="3448050"/>
+        </a:xfrm>
+      </xdr:grpSpPr>
+      <xdr:pic>
+        <xdr:nvPicPr>
+          <xdr:cNvPr id="78" name="図 77">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B6115243-160D-D2AD-F710-43CE134BC670}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvPicPr>
+            <a:picLocks noChangeAspect="1"/>
+          </xdr:cNvPicPr>
+        </xdr:nvPicPr>
+        <xdr:blipFill>
+          <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
+          <a:stretch>
+            <a:fillRect/>
+          </a:stretch>
+        </xdr:blipFill>
+        <xdr:spPr>
+          <a:xfrm>
+            <a:off x="990600" y="46167675"/>
+            <a:ext cx="3000375" cy="495300"/>
+          </a:xfrm>
+          <a:prstGeom prst="rect">
+            <a:avLst/>
+          </a:prstGeom>
+        </xdr:spPr>
+      </xdr:pic>
+      <xdr:grpSp>
+        <xdr:nvGrpSpPr>
+          <xdr:cNvPr id="67" name="グループ化 66">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3900DA7E-A893-1BFF-4DD0-EFF5468D7074}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvGrpSpPr/>
+        </xdr:nvGrpSpPr>
+        <xdr:grpSpPr>
+          <a:xfrm>
+            <a:off x="990600" y="43214925"/>
+            <a:ext cx="2962275" cy="2962275"/>
+            <a:chOff x="742950" y="8524875"/>
+            <a:chExt cx="2962275" cy="2962275"/>
+          </a:xfrm>
+        </xdr:grpSpPr>
+        <xdr:grpSp>
+          <xdr:nvGrpSpPr>
+            <xdr:cNvPr id="68" name="グループ化 67">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F23A33FE-14F9-DDBB-D51B-2E7EDD4E6096}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvGrpSpPr/>
+          </xdr:nvGrpSpPr>
+          <xdr:grpSpPr>
+            <a:xfrm>
+              <a:off x="742950" y="8524875"/>
+              <a:ext cx="2962275" cy="2962275"/>
+              <a:chOff x="742950" y="8524875"/>
+              <a:chExt cx="2962275" cy="2962275"/>
+            </a:xfrm>
+          </xdr:grpSpPr>
+          <xdr:pic>
+            <xdr:nvPicPr>
+              <xdr:cNvPr id="70" name="図 69">
+                <a:extLst>
+                  <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                    <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{66B0A000-C7F3-CA6E-9A38-5F96BC04CB9F}"/>
+                  </a:ext>
+                </a:extLst>
+              </xdr:cNvPr>
+              <xdr:cNvPicPr>
+                <a:picLocks noChangeAspect="1"/>
+              </xdr:cNvPicPr>
+            </xdr:nvPicPr>
+            <xdr:blipFill>
+              <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+              <a:stretch>
+                <a:fillRect/>
+              </a:stretch>
+            </xdr:blipFill>
+            <xdr:spPr>
+              <a:xfrm>
+                <a:off x="742950" y="8524875"/>
+                <a:ext cx="2962275" cy="2962275"/>
+              </a:xfrm>
+              <a:prstGeom prst="rect">
+                <a:avLst/>
+              </a:prstGeom>
+            </xdr:spPr>
+          </xdr:pic>
+          <xdr:pic>
+            <xdr:nvPicPr>
+              <xdr:cNvPr id="71" name="図 70">
+                <a:extLst>
+                  <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                    <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{82F4C319-476E-6538-D302-FABBFF99D396}"/>
+                  </a:ext>
+                </a:extLst>
+              </xdr:cNvPr>
+              <xdr:cNvPicPr>
+                <a:picLocks noChangeAspect="1"/>
+              </xdr:cNvPicPr>
+            </xdr:nvPicPr>
+            <xdr:blipFill>
+              <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+              <a:stretch>
+                <a:fillRect/>
+              </a:stretch>
+            </xdr:blipFill>
+            <xdr:spPr>
+              <a:xfrm>
+                <a:off x="1514475" y="10058400"/>
+                <a:ext cx="1619250" cy="238158"/>
+              </a:xfrm>
+              <a:prstGeom prst="rect">
+                <a:avLst/>
+              </a:prstGeom>
+            </xdr:spPr>
+          </xdr:pic>
+        </xdr:grpSp>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="69" name="テキスト ボックス 68">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1E326EFE-446C-DEE3-5368-F33832E1E0DE}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr txBox="1"/>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="1257300" y="9258300"/>
+              <a:ext cx="2080570" cy="1469954"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+          </xdr:spPr>
+          <xdr:style>
+            <a:lnRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:lnRef>
+            <a:fillRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:fillRef>
+            <a:effectRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:effectRef>
+            <a:fontRef idx="minor">
+              <a:schemeClr val="tx1"/>
+            </a:fontRef>
+          </xdr:style>
+          <xdr:txBody>
+            <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="none" rtlCol="0" anchor="t">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:r>
+                <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="8800"/>
+                <a:t>30</a:t>
+              </a:r>
+              <a:r>
+                <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="4800"/>
+                <a:t>cm</a:t>
+              </a:r>
+              <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="8800"/>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+      </xdr:grpSp>
+      <xdr:cxnSp macro="">
+        <xdr:nvCxnSpPr>
+          <xdr:cNvPr id="72" name="直線コネクタ 71">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{CE732624-AD11-25DD-E26D-D50B2CAF831B}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvCxnSpPr/>
+        </xdr:nvCxnSpPr>
+        <xdr:spPr>
+          <a:xfrm flipV="1">
+            <a:off x="1752600" y="45700950"/>
+            <a:ext cx="657225" cy="466725"/>
+          </a:xfrm>
+          <a:prstGeom prst="line">
+            <a:avLst/>
+          </a:prstGeom>
+          <a:ln w="34925">
+            <a:solidFill>
+              <a:srgbClr val="FF0000"/>
+            </a:solidFill>
+          </a:ln>
+        </xdr:spPr>
+        <xdr:style>
+          <a:lnRef idx="1">
+            <a:schemeClr val="accent1"/>
+          </a:lnRef>
+          <a:fillRef idx="0">
+            <a:schemeClr val="accent1"/>
+          </a:fillRef>
+          <a:effectRef idx="0">
+            <a:schemeClr val="accent1"/>
+          </a:effectRef>
+          <a:fontRef idx="minor">
+            <a:schemeClr val="tx1"/>
+          </a:fontRef>
+        </xdr:style>
+      </xdr:cxnSp>
+      <xdr:sp macro="" textlink="">
+        <xdr:nvSpPr>
+          <xdr:cNvPr id="73" name="テキスト ボックス 72">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{EB2422C9-68AE-A3B0-E412-2EADA6715A34}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvSpPr txBox="1"/>
+        </xdr:nvSpPr>
+        <xdr:spPr>
+          <a:xfrm>
+            <a:off x="971550" y="46253400"/>
+            <a:ext cx="607859" cy="328423"/>
+          </a:xfrm>
+          <a:prstGeom prst="rect">
+            <a:avLst/>
+          </a:prstGeom>
+          <a:noFill/>
+        </xdr:spPr>
+        <xdr:style>
+          <a:lnRef idx="0">
+            <a:scrgbClr r="0" g="0" b="0"/>
+          </a:lnRef>
+          <a:fillRef idx="0">
+            <a:scrgbClr r="0" g="0" b="0"/>
+          </a:fillRef>
+          <a:effectRef idx="0">
+            <a:scrgbClr r="0" g="0" b="0"/>
+          </a:effectRef>
+          <a:fontRef idx="minor">
+            <a:schemeClr val="tx1"/>
+          </a:fontRef>
+        </xdr:style>
+        <xdr:txBody>
+          <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="none" rtlCol="0" anchor="t">
+            <a:spAutoFit/>
+          </a:bodyPr>
+          <a:lstStyle/>
+          <a:p>
+            <a:r>
+              <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+              <a:t>距離：</a:t>
+            </a:r>
+          </a:p>
+        </xdr:txBody>
+      </xdr:sp>
+      <xdr:sp macro="" textlink="">
+        <xdr:nvSpPr>
+          <xdr:cNvPr id="74" name="テキスト ボックス 73">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{849AE6F0-B4BC-8384-4376-CB2C7F473D0B}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvSpPr txBox="1"/>
+        </xdr:nvSpPr>
+        <xdr:spPr>
+          <a:xfrm>
+            <a:off x="1457326" y="46262925"/>
+            <a:ext cx="419100" cy="304800"/>
+          </a:xfrm>
+          <a:prstGeom prst="rect">
+            <a:avLst/>
+          </a:prstGeom>
+          <a:solidFill>
+            <a:schemeClr val="lt1"/>
+          </a:solidFill>
+          <a:ln w="9525" cmpd="sng">
+            <a:solidFill>
+              <a:schemeClr val="lt1">
+                <a:shade val="50000"/>
+              </a:schemeClr>
+            </a:solidFill>
+          </a:ln>
+        </xdr:spPr>
+        <xdr:style>
+          <a:lnRef idx="0">
+            <a:scrgbClr r="0" g="0" b="0"/>
+          </a:lnRef>
+          <a:fillRef idx="0">
+            <a:scrgbClr r="0" g="0" b="0"/>
+          </a:fillRef>
+          <a:effectRef idx="0">
+            <a:scrgbClr r="0" g="0" b="0"/>
+          </a:effectRef>
+          <a:fontRef idx="minor">
+            <a:schemeClr val="dk1"/>
+          </a:fontRef>
+        </xdr:style>
+        <xdr:txBody>
+          <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+          </a:p>
+        </xdr:txBody>
+      </xdr:sp>
+      <xdr:sp macro="" textlink="">
+        <xdr:nvSpPr>
+          <xdr:cNvPr id="75" name="テキスト ボックス 74">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A0E05162-C9A7-8B42-64F7-2F396CF06469}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvSpPr txBox="1"/>
+        </xdr:nvSpPr>
+        <xdr:spPr>
+          <a:xfrm>
+            <a:off x="1838325" y="46253400"/>
+            <a:ext cx="748923" cy="328423"/>
+          </a:xfrm>
+          <a:prstGeom prst="rect">
+            <a:avLst/>
+          </a:prstGeom>
+          <a:noFill/>
+        </xdr:spPr>
+        <xdr:style>
+          <a:lnRef idx="0">
+            <a:scrgbClr r="0" g="0" b="0"/>
+          </a:lnRef>
+          <a:fillRef idx="0">
+            <a:scrgbClr r="0" g="0" b="0"/>
+          </a:fillRef>
+          <a:effectRef idx="0">
+            <a:scrgbClr r="0" g="0" b="0"/>
+          </a:effectRef>
+          <a:fontRef idx="minor">
+            <a:schemeClr val="tx1"/>
+          </a:fontRef>
+        </xdr:style>
+        <xdr:txBody>
+          <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="none" rtlCol="0" anchor="t">
+            <a:spAutoFit/>
+          </a:bodyPr>
+          <a:lstStyle/>
+          <a:p>
+            <a:r>
+              <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+              <a:t>経過秒：</a:t>
+            </a:r>
+          </a:p>
+        </xdr:txBody>
+      </xdr:sp>
+      <xdr:sp macro="" textlink="">
+        <xdr:nvSpPr>
+          <xdr:cNvPr id="76" name="テキスト ボックス 75">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{43B86C34-AF68-ADD1-4932-F5EDB869F086}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvSpPr txBox="1"/>
+        </xdr:nvSpPr>
+        <xdr:spPr>
+          <a:xfrm>
+            <a:off x="2466975" y="46262925"/>
+            <a:ext cx="504825" cy="304800"/>
+          </a:xfrm>
+          <a:prstGeom prst="rect">
+            <a:avLst/>
+          </a:prstGeom>
+          <a:solidFill>
+            <a:schemeClr val="lt1"/>
+          </a:solidFill>
+          <a:ln w="9525" cmpd="sng">
+            <a:solidFill>
+              <a:schemeClr val="lt1">
+                <a:shade val="50000"/>
+              </a:schemeClr>
+            </a:solidFill>
+          </a:ln>
+        </xdr:spPr>
+        <xdr:style>
+          <a:lnRef idx="0">
+            <a:scrgbClr r="0" g="0" b="0"/>
+          </a:lnRef>
+          <a:fillRef idx="0">
+            <a:scrgbClr r="0" g="0" b="0"/>
+          </a:fillRef>
+          <a:effectRef idx="0">
+            <a:scrgbClr r="0" g="0" b="0"/>
+          </a:effectRef>
+          <a:fontRef idx="minor">
+            <a:schemeClr val="dk1"/>
+          </a:fontRef>
+        </xdr:style>
+        <xdr:txBody>
+          <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+          </a:p>
+        </xdr:txBody>
+      </xdr:sp>
+      <xdr:sp macro="" textlink="">
+        <xdr:nvSpPr>
+          <xdr:cNvPr id="77" name="テキスト ボックス 76">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4F160341-1EB6-4CAA-0DB6-D438467F4B2B}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvSpPr txBox="1"/>
+        </xdr:nvSpPr>
+        <xdr:spPr>
+          <a:xfrm>
+            <a:off x="3086100" y="46262925"/>
+            <a:ext cx="800100" cy="304800"/>
+          </a:xfrm>
+          <a:prstGeom prst="rect">
+            <a:avLst/>
+          </a:prstGeom>
+          <a:solidFill>
+            <a:schemeClr val="bg1">
+              <a:lumMod val="95000"/>
+            </a:schemeClr>
+          </a:solidFill>
+          <a:ln w="9525" cmpd="sng">
+            <a:solidFill>
+              <a:schemeClr val="lt1">
+                <a:shade val="50000"/>
+              </a:schemeClr>
+            </a:solidFill>
+          </a:ln>
+        </xdr:spPr>
+        <xdr:style>
+          <a:lnRef idx="0">
+            <a:scrgbClr r="0" g="0" b="0"/>
+          </a:lnRef>
+          <a:fillRef idx="0">
+            <a:scrgbClr r="0" g="0" b="0"/>
+          </a:fillRef>
+          <a:effectRef idx="0">
+            <a:scrgbClr r="0" g="0" b="0"/>
+          </a:effectRef>
+          <a:fontRef idx="minor">
+            <a:schemeClr val="dk1"/>
+          </a:fontRef>
+        </xdr:style>
+        <xdr:txBody>
+          <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="ctr"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr algn="ctr"/>
+            <a:r>
+              <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1600"/>
+              <a:t>Set</a:t>
+            </a:r>
+            <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1600"/>
+          </a:p>
+        </xdr:txBody>
+      </xdr:sp>
+    </xdr:grpSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
 </xdr:wsDr>
 </file>
 
@@ -3110,7 +4431,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{65C45921-06FE-4B81-BC0C-E57414EB5CD4}">
-  <dimension ref="A1:Q93"/>
+  <dimension ref="A1:S214"/>
   <sheetFormatPr defaultColWidth="3.25" defaultRowHeight="18.75"/>
   <sheetData>
     <row r="1" spans="1:3" s="12" customFormat="1" ht="18">
@@ -3172,7 +4493,7 @@
       </c>
     </row>
     <row r="55" spans="1:10">
-      <c r="B55" t="s">
+      <c r="B55" s="13" t="s">
         <v>19</v>
       </c>
     </row>
@@ -3180,7 +4501,7 @@
       <c r="C57" s="14" t="s">
         <v>21</v>
       </c>
-      <c r="D57" t="s">
+      <c r="D57" s="13" t="s">
         <v>20</v>
       </c>
     </row>
@@ -3201,158 +4522,574 @@
     </row>
     <row r="62" spans="1:10">
       <c r="F62" t="s">
-        <v>24</v>
-      </c>
-      <c r="J62" t="s">
-        <v>28</v>
+        <v>85</v>
       </c>
     </row>
     <row r="63" spans="1:10">
       <c r="F63" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="J63" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="64" spans="1:10">
       <c r="F64" t="s">
+        <v>25</v>
+      </c>
+      <c r="J64" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="65" spans="2:12">
+      <c r="F65" t="s">
+        <v>37</v>
+      </c>
+      <c r="J65" t="s">
         <v>38</v>
       </c>
-      <c r="J64" t="s">
+      <c r="L65" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="66" spans="2:12">
+      <c r="E66" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="68" spans="2:12">
+      <c r="B68" s="13" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="70" spans="2:12">
+      <c r="C70" s="14" t="s">
+        <v>21</v>
+      </c>
+      <c r="D70" s="13" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="72" spans="2:12">
+      <c r="D72" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="73" spans="2:12">
+      <c r="E73" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="74" spans="2:12">
+      <c r="F74" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="75" spans="2:12">
+      <c r="F75" t="s">
+        <v>24</v>
+      </c>
+      <c r="J75" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="76" spans="2:12">
+      <c r="F76" t="s">
+        <v>25</v>
+      </c>
+      <c r="J76" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="77" spans="2:12">
+      <c r="F77" t="s">
+        <v>37</v>
+      </c>
+      <c r="J77" t="s">
+        <v>38</v>
+      </c>
+      <c r="L77" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="78" spans="2:12">
+      <c r="E78" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="80" spans="2:12">
+      <c r="D80" t="s">
+        <v>35</v>
+      </c>
+      <c r="E80" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="82" spans="4:15">
+      <c r="E82" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="83" spans="4:15">
+      <c r="F83" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="84" spans="4:15">
+      <c r="F84" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="85" spans="4:15">
+      <c r="F85" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="65" spans="2:5">
-      <c r="E65" t="s">
+    <row r="86" spans="4:15">
+      <c r="F86" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="88" spans="4:15">
+      <c r="D88" t="s">
+        <v>34</v>
+      </c>
+      <c r="E88" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="90" spans="4:15">
+      <c r="E90" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="91" spans="4:15">
+      <c r="E91" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="93" spans="4:15">
+      <c r="D93" t="s">
+        <v>43</v>
+      </c>
+      <c r="E93" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="95" spans="4:15">
+      <c r="E95" t="s">
+        <v>45</v>
+      </c>
+      <c r="O95" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="97" spans="3:17">
+      <c r="F97" t="s">
+        <v>23</v>
+      </c>
+      <c r="P97" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="98" spans="3:17">
+      <c r="F98" t="s">
+        <v>27</v>
+      </c>
+      <c r="P98" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="99" spans="3:17">
+      <c r="G99" t="s">
+        <v>74</v>
+      </c>
+      <c r="Q99" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="100" spans="3:17">
+      <c r="G100" t="s">
+        <v>44</v>
+      </c>
+      <c r="Q100" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="101" spans="3:17">
+      <c r="G101" t="s">
+        <v>47</v>
+      </c>
+      <c r="Q101" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="102" spans="3:17">
+      <c r="G102" t="s">
+        <v>86</v>
+      </c>
+      <c r="Q102" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="103" spans="3:17">
+      <c r="F103" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="67" spans="2:5">
-      <c r="B67" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="69" spans="2:5">
-      <c r="C69" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="71" spans="2:5">
-      <c r="D71" t="s">
-        <v>36</v>
-      </c>
-      <c r="E71" t="s">
+      <c r="P103" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="105" spans="3:17">
+      <c r="C105" s="14" t="s">
+        <v>21</v>
+      </c>
+      <c r="D105" s="13" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="107" spans="3:17">
+      <c r="E107" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="108" spans="3:17">
+      <c r="E108" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="109" spans="3:17">
+      <c r="F109" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="110" spans="3:17">
+      <c r="E110" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="112" spans="3:17">
+      <c r="E112" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="113" spans="3:10">
+      <c r="F113" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="115" spans="3:10">
+      <c r="C115" s="14" t="s">
+        <v>21</v>
+      </c>
+      <c r="D115" s="13" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="117" spans="3:10">
+      <c r="E117" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="118" spans="3:10">
+      <c r="E118" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="119" spans="3:10">
+      <c r="F119" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="120" spans="3:10">
+      <c r="F120" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="121" spans="3:10">
+      <c r="F121" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="122" spans="3:10">
+      <c r="F122" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="123" spans="3:10">
+      <c r="E123" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="125" spans="3:10">
+      <c r="E125" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="127" spans="3:10">
+      <c r="E127" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="128" spans="3:10">
+      <c r="F128" t="s">
         <v>32</v>
       </c>
-    </row>
-    <row r="73" spans="2:5">
-      <c r="E73" t="s">
+      <c r="J128" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="129" spans="3:10">
+      <c r="F129" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="74" spans="2:5">
-      <c r="E74" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="75" spans="2:5">
-      <c r="E75" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="76" spans="2:5">
-      <c r="E76" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="78" spans="2:5">
-      <c r="D78" t="s">
-        <v>35</v>
-      </c>
-      <c r="E78" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="80" spans="2:5">
-      <c r="E80" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="81" spans="4:17">
-      <c r="E81" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="83" spans="4:17">
-      <c r="D83" t="s">
+      <c r="J129" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="130" spans="3:10">
+      <c r="F130" t="s">
+        <v>39</v>
+      </c>
+      <c r="J130" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="132" spans="3:10">
+      <c r="C132" s="14" t="s">
+        <v>21</v>
+      </c>
+      <c r="D132" s="13" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="134" spans="3:10">
+      <c r="E134" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="135" spans="3:10">
+      <c r="E135" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="136" spans="3:10">
+      <c r="F136" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="137" spans="3:10">
+      <c r="F137" t="s">
         <v>44</v>
       </c>
-      <c r="E83" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="85" spans="4:17">
-      <c r="E85" t="s">
-        <v>47</v>
-      </c>
-      <c r="O85" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="87" spans="4:17">
-      <c r="F87" t="s">
+    </row>
+    <row r="138" spans="3:10">
+      <c r="E138" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="140" spans="3:10">
+      <c r="E140" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="142" spans="3:10">
+      <c r="E142" t="s">
         <v>23</v>
       </c>
-      <c r="P87" t="s">
+    </row>
+    <row r="143" spans="3:10">
+      <c r="E143" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="144" spans="3:10">
+      <c r="F144" t="s">
+        <v>89</v>
+      </c>
+      <c r="J144" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="145" spans="2:11">
+      <c r="F145" t="s">
+        <v>32</v>
+      </c>
+      <c r="J145" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="146" spans="2:11">
+      <c r="F146" t="s">
+        <v>53</v>
+      </c>
+      <c r="J146" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="147" spans="2:11">
+      <c r="F147" t="s">
+        <v>39</v>
+      </c>
+      <c r="J147" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="148" spans="2:11">
+      <c r="E148" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="150" spans="2:11">
+      <c r="E150" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="152" spans="2:11">
+      <c r="E152" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="153" spans="2:11">
+      <c r="F153" t="s">
+        <v>66</v>
+      </c>
+      <c r="K153" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="154" spans="2:11">
+      <c r="F154" t="s">
+        <v>67</v>
+      </c>
+      <c r="K154" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="156" spans="2:11">
+      <c r="B156" s="13" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="158" spans="2:11">
+      <c r="C158" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="D158" s="13" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="160" spans="2:11">
+      <c r="D160" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="88" spans="4:17">
-      <c r="F88" t="s">
+    <row r="161" spans="3:19">
+      <c r="D161" t="s">
         <v>27</v>
       </c>
-      <c r="P88" t="s">
+    </row>
+    <row r="162" spans="3:19">
+      <c r="E162" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="163" spans="3:19">
+      <c r="D163" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="165" spans="3:19">
+      <c r="D165" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="166" spans="3:19">
+      <c r="D166" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="89" spans="4:17">
-      <c r="G89" t="s">
-        <v>49</v>
-      </c>
-      <c r="Q89" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="90" spans="4:17">
-      <c r="G90" t="s">
-        <v>45</v>
-      </c>
-      <c r="Q90" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="91" spans="4:17">
-      <c r="G91" t="s">
-        <v>51</v>
-      </c>
-      <c r="Q91" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="92" spans="4:17">
-      <c r="G92" t="s">
-        <v>50</v>
-      </c>
-      <c r="Q92" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="93" spans="4:17">
-      <c r="F93" t="s">
+    <row r="167" spans="3:19">
+      <c r="E167" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="168" spans="3:19">
+      <c r="E168" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="169" spans="3:19">
+      <c r="E169" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="170" spans="3:19">
+      <c r="E170" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="171" spans="3:19">
+      <c r="D171" t="s">
         <v>26</v>
       </c>
-      <c r="P93" t="s">
+    </row>
+    <row r="173" spans="3:19">
+      <c r="C173" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="D173" s="13" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="175" spans="3:19">
+      <c r="D175" t="s">
+        <v>81</v>
+      </c>
+      <c r="S175" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="191" spans="3:4">
+      <c r="C191" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="D191" s="13" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="208" spans="5:5">
+      <c r="E208" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="209" spans="5:6">
+      <c r="E209" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="210" spans="5:6">
+      <c r="F210" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="211" spans="5:6">
+      <c r="F211" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="212" spans="5:6">
+      <c r="F212" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="213" spans="5:6">
+      <c r="F213" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="214" spans="5:6">
+      <c r="E214" t="s">
         <v>26</v>
       </c>
     </row>

--- a/設計書.xlsx
+++ b/設計書.xlsx
@@ -8,13 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\ikura\次世代開発\ソース\CounterServer\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{35D7A7B2-A6AC-440B-8A67-400FD2427ED6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{20EBFCCA-08EB-4B70-98BA-81E7B9A85F5A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="レイアウト" sheetId="1" r:id="rId1"/>
     <sheet name="設計書_距離" sheetId="2" r:id="rId2"/>
+    <sheet name="テーブル" sheetId="3" r:id="rId3"/>
+    <sheet name="環境設定ファイル" sheetId="4" r:id="rId4"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -26,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="155" uniqueCount="91">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="256" uniqueCount="149">
   <si>
     <t>Home</t>
     <phoneticPr fontId="1"/>
@@ -878,6 +880,421 @@
   </si>
   <si>
     <t>"distenv"</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>テーブル名</t>
+    <rPh sb="4" eb="5">
+      <t>メイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>設定テーブル</t>
+    <rPh sb="0" eb="2">
+      <t>セッテイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>フィールド名</t>
+    <rPh sb="5" eb="6">
+      <t>メイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>日本語名</t>
+    <rPh sb="0" eb="4">
+      <t>ニホンゴメイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>id</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>型</t>
+    <rPh sb="0" eb="1">
+      <t>カタ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>AutoNumber</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>キー</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>〇</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>成型機番号</t>
+    <rPh sb="0" eb="3">
+      <t>セイケイキ</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>バンゴウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>DBファイル名</t>
+    <rPh sb="6" eb="7">
+      <t>メイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>data_store.db</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>経過時間（秒）</t>
+    <rPh sb="0" eb="4">
+      <t>ケイカジカン</t>
+    </rPh>
+    <rPh sb="5" eb="6">
+      <t>ビョウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>警告距離（cm）</t>
+    <rPh sb="0" eb="2">
+      <t>ケイコク</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>キョリ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>integer</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>保存日時</t>
+    <rPh sb="0" eb="4">
+      <t>ホゾンニチジ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>timestamp</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>役割</t>
+    <rPh sb="0" eb="2">
+      <t>ヤクワリ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>成型機毎の警告距離と経過時間の設定を保存する</t>
+    <rPh sb="0" eb="3">
+      <t>セイケイキ</t>
+    </rPh>
+    <rPh sb="3" eb="4">
+      <t>ゴト</t>
+    </rPh>
+    <rPh sb="5" eb="9">
+      <t>ケイコクキョリ</t>
+    </rPh>
+    <rPh sb="10" eb="14">
+      <t>ケイカジカン</t>
+    </rPh>
+    <rPh sb="15" eb="17">
+      <t>セッテイ</t>
+    </rPh>
+    <rPh sb="18" eb="20">
+      <t>ホゾン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>備考</t>
+    <rPh sb="0" eb="2">
+      <t>ビコウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>距離保存テーブル</t>
+    <rPh sb="0" eb="2">
+      <t>キョリ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>ホゾン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>成型機毎に計測した距離と経過時間を保存する</t>
+    <rPh sb="0" eb="3">
+      <t>セイケイキ</t>
+    </rPh>
+    <rPh sb="3" eb="4">
+      <t>ゴト</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>ケイソク</t>
+    </rPh>
+    <rPh sb="9" eb="11">
+      <t>キョリ</t>
+    </rPh>
+    <rPh sb="12" eb="16">
+      <t>ケイカジカン</t>
+    </rPh>
+    <rPh sb="17" eb="19">
+      <t>ホゾン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>CounterServerの設定ファイル</t>
+    <rPh sb="14" eb="16">
+      <t>セッテイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>場所</t>
+    <rPh sb="0" eb="2">
+      <t>バショ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>CounterServer</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>└ .env</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>内容</t>
+    <rPh sb="0" eb="2">
+      <t>ナイヨウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>名称</t>
+    <rPh sb="0" eb="2">
+      <t>メイショウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>DB_NAME</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>データベースファイル名</t>
+    <rPh sb="10" eb="11">
+      <t>メイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>意味</t>
+    <rPh sb="0" eb="2">
+      <t>イミ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>PORT_NO</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>LOG_DIR</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ログファイルの保存フォルダ</t>
+    <rPh sb="7" eb="9">
+      <t>ホゾン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>LOG_NAME</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ログファイル名称</t>
+    <rPh sb="6" eb="8">
+      <t>メイショウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>READ_TIME</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>設定値</t>
+    <rPh sb="0" eb="3">
+      <t>セッテイアタイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>./app</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>server.log</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>距離テーブルを参照するときの時間間隔（秒）</t>
+    <rPh sb="0" eb="2">
+      <t>キョリ</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>サンショウ</t>
+    </rPh>
+    <rPh sb="14" eb="18">
+      <t>ジカンカンカク</t>
+    </rPh>
+    <rPh sb="19" eb="20">
+      <t>ビョウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>INIT_DISTANCE</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>警告を表示するときの距離（cm）</t>
+    <rPh sb="0" eb="2">
+      <t>ケイコク</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>ヒョウジ</t>
+    </rPh>
+    <rPh sb="10" eb="12">
+      <t>キョリ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>警告を表示するときの秒数（秒）</t>
+    <rPh sb="0" eb="2">
+      <t>ケイコク</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>ヒョウジ</t>
+    </rPh>
+    <rPh sb="10" eb="12">
+      <t>ビョウスウ</t>
+    </rPh>
+    <rPh sb="13" eb="14">
+      <t>ビョウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>SLACK_WEBHOOK_URL</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>SLACK_SEND_INTERVAL</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>https://hooks.slack.com/services/************</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>SlackのWebhookのURL</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Slackへ通知してから再度通知するまでの間隔（秒）</t>
+    <rPh sb="6" eb="8">
+      <t>ツウチ</t>
+    </rPh>
+    <rPh sb="12" eb="14">
+      <t>サイド</t>
+    </rPh>
+    <rPh sb="14" eb="16">
+      <t>ツウチ</t>
+    </rPh>
+    <rPh sb="21" eb="23">
+      <t>カンカク</t>
+    </rPh>
+    <rPh sb="24" eb="25">
+      <t>ビョウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Webサーバの設定ファイル</t>
+    <rPh sb="7" eb="9">
+      <t>セッテイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>CounterServer\web</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Webサーバのポート番号</t>
+    <rPh sb="10" eb="12">
+      <t>バンゴウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>CounterServer起動時のPort番号</t>
+    <rPh sb="13" eb="16">
+      <t>キドウジ</t>
+    </rPh>
+    <rPh sb="21" eb="23">
+      <t>バンゴウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>SERVER_WS_URL</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ws://localhost:8765</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>CounterServerのWebSocketのURL</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>LINE_MAX</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>表示する成型機の台数</t>
+    <rPh sb="0" eb="2">
+      <t>ヒョウジ</t>
+    </rPh>
+    <rPh sb="4" eb="7">
+      <t>セイケイキ</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>ダイスウ</t>
+    </rPh>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -885,7 +1302,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3">
+  <fonts count="5">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -909,8 +1326,25 @@
       <charset val="128"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="14"/>
+      <color theme="1"/>
+      <name val="Yu Gothic"/>
+      <family val="3"/>
+      <charset val="128"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <color theme="1"/>
+      <name val="Yu Gothic"/>
+      <family val="3"/>
+      <charset val="128"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -923,8 +1357,26 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.39997558519241921"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="12">
+  <borders count="13">
     <border>
       <left/>
       <right/>
@@ -1049,11 +1501,26 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="38">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
@@ -1070,6 +1537,63 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" indent="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -5098,4 +5622,523 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F0FE54D6-3349-41AE-982E-18597B59E794}">
+  <dimension ref="A1:E25"/>
+  <sheetFormatPr defaultRowHeight="18.75"/>
+  <cols>
+    <col min="1" max="1" width="17.375" customWidth="1"/>
+    <col min="2" max="2" width="21.375" customWidth="1"/>
+    <col min="3" max="3" width="14" customWidth="1"/>
+    <col min="4" max="4" width="6.5" style="15" customWidth="1"/>
+    <col min="5" max="5" width="20.5" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" s="20" customFormat="1" ht="35.25" customHeight="1">
+      <c r="A1" s="21" t="s">
+        <v>101</v>
+      </c>
+      <c r="B1" s="19" t="s">
+        <v>102</v>
+      </c>
+      <c r="D1" s="24"/>
+    </row>
+    <row r="3" spans="1:5">
+      <c r="A3" s="22" t="s">
+        <v>91</v>
+      </c>
+      <c r="B3" s="16" t="s">
+        <v>55</v>
+      </c>
+      <c r="C3" s="22" t="s">
+        <v>94</v>
+      </c>
+      <c r="D3" s="25" t="s">
+        <v>92</v>
+      </c>
+      <c r="E3" s="26"/>
+    </row>
+    <row r="4" spans="1:5">
+      <c r="A4" s="23" t="s">
+        <v>108</v>
+      </c>
+      <c r="B4" s="23"/>
+      <c r="C4" s="23"/>
+      <c r="D4" s="23"/>
+      <c r="E4" s="23"/>
+    </row>
+    <row r="5" spans="1:5" ht="48" customHeight="1">
+      <c r="A5" s="17" t="s">
+        <v>109</v>
+      </c>
+      <c r="B5" s="17"/>
+      <c r="C5" s="17"/>
+      <c r="D5" s="17"/>
+      <c r="E5" s="17"/>
+    </row>
+    <row r="6" spans="1:5">
+      <c r="A6" s="22" t="s">
+        <v>93</v>
+      </c>
+      <c r="B6" s="22" t="s">
+        <v>94</v>
+      </c>
+      <c r="C6" s="22" t="s">
+        <v>96</v>
+      </c>
+      <c r="D6" s="22" t="s">
+        <v>98</v>
+      </c>
+      <c r="E6" s="22" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5">
+      <c r="A7" s="16" t="s">
+        <v>95</v>
+      </c>
+      <c r="B7" s="16" t="s">
+        <v>95</v>
+      </c>
+      <c r="C7" s="16" t="s">
+        <v>97</v>
+      </c>
+      <c r="D7" s="18" t="s">
+        <v>99</v>
+      </c>
+      <c r="E7" s="16"/>
+    </row>
+    <row r="8" spans="1:5">
+      <c r="A8" s="16" t="s">
+        <v>32</v>
+      </c>
+      <c r="B8" s="16" t="s">
+        <v>100</v>
+      </c>
+      <c r="C8" s="16" t="s">
+        <v>105</v>
+      </c>
+      <c r="D8" s="18"/>
+      <c r="E8" s="16"/>
+    </row>
+    <row r="9" spans="1:5">
+      <c r="A9" s="16" t="s">
+        <v>33</v>
+      </c>
+      <c r="B9" s="16" t="s">
+        <v>104</v>
+      </c>
+      <c r="C9" s="16" t="s">
+        <v>105</v>
+      </c>
+      <c r="D9" s="18"/>
+      <c r="E9" s="16"/>
+    </row>
+    <row r="10" spans="1:5">
+      <c r="A10" s="16" t="s">
+        <v>39</v>
+      </c>
+      <c r="B10" s="16" t="s">
+        <v>103</v>
+      </c>
+      <c r="C10" s="16" t="s">
+        <v>105</v>
+      </c>
+      <c r="D10" s="18"/>
+      <c r="E10" s="16"/>
+    </row>
+    <row r="11" spans="1:5">
+      <c r="A11" s="16" t="s">
+        <v>40</v>
+      </c>
+      <c r="B11" s="16" t="s">
+        <v>106</v>
+      </c>
+      <c r="C11" s="16" t="s">
+        <v>107</v>
+      </c>
+      <c r="D11" s="18"/>
+      <c r="E11" s="16"/>
+    </row>
+    <row r="12" spans="1:5">
+      <c r="A12" s="16"/>
+      <c r="B12" s="16"/>
+      <c r="C12" s="16"/>
+      <c r="D12" s="18"/>
+      <c r="E12" s="16"/>
+    </row>
+    <row r="13" spans="1:5">
+      <c r="A13" s="27"/>
+      <c r="B13" s="27"/>
+      <c r="C13" s="27"/>
+      <c r="D13" s="28"/>
+      <c r="E13" s="27"/>
+    </row>
+    <row r="14" spans="1:5" s="29" customFormat="1">
+      <c r="D14" s="30"/>
+    </row>
+    <row r="16" spans="1:5">
+      <c r="A16" s="22" t="s">
+        <v>91</v>
+      </c>
+      <c r="B16" s="16" t="s">
+        <v>54</v>
+      </c>
+      <c r="C16" s="22" t="s">
+        <v>94</v>
+      </c>
+      <c r="D16" s="25" t="s">
+        <v>111</v>
+      </c>
+      <c r="E16" s="26"/>
+    </row>
+    <row r="17" spans="1:5">
+      <c r="A17" s="23" t="s">
+        <v>108</v>
+      </c>
+      <c r="B17" s="23"/>
+      <c r="C17" s="23"/>
+      <c r="D17" s="23"/>
+      <c r="E17" s="23"/>
+    </row>
+    <row r="18" spans="1:5" ht="48" customHeight="1">
+      <c r="A18" s="17" t="s">
+        <v>112</v>
+      </c>
+      <c r="B18" s="17"/>
+      <c r="C18" s="17"/>
+      <c r="D18" s="17"/>
+      <c r="E18" s="17"/>
+    </row>
+    <row r="19" spans="1:5">
+      <c r="A19" s="22" t="s">
+        <v>93</v>
+      </c>
+      <c r="B19" s="22" t="s">
+        <v>94</v>
+      </c>
+      <c r="C19" s="22" t="s">
+        <v>96</v>
+      </c>
+      <c r="D19" s="22" t="s">
+        <v>98</v>
+      </c>
+      <c r="E19" s="22" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5">
+      <c r="A20" s="16" t="s">
+        <v>95</v>
+      </c>
+      <c r="B20" s="16" t="s">
+        <v>95</v>
+      </c>
+      <c r="C20" s="16" t="s">
+        <v>97</v>
+      </c>
+      <c r="D20" s="18" t="s">
+        <v>99</v>
+      </c>
+      <c r="E20" s="16"/>
+    </row>
+    <row r="21" spans="1:5">
+      <c r="A21" s="16" t="s">
+        <v>32</v>
+      </c>
+      <c r="B21" s="16" t="s">
+        <v>100</v>
+      </c>
+      <c r="C21" s="16" t="s">
+        <v>105</v>
+      </c>
+      <c r="D21" s="18"/>
+      <c r="E21" s="16"/>
+    </row>
+    <row r="22" spans="1:5">
+      <c r="A22" s="16" t="s">
+        <v>33</v>
+      </c>
+      <c r="B22" s="16" t="s">
+        <v>104</v>
+      </c>
+      <c r="C22" s="16" t="s">
+        <v>105</v>
+      </c>
+      <c r="D22" s="18"/>
+      <c r="E22" s="16"/>
+    </row>
+    <row r="23" spans="1:5">
+      <c r="A23" s="16" t="s">
+        <v>39</v>
+      </c>
+      <c r="B23" s="16" t="s">
+        <v>103</v>
+      </c>
+      <c r="C23" s="16" t="s">
+        <v>105</v>
+      </c>
+      <c r="D23" s="18"/>
+      <c r="E23" s="16"/>
+    </row>
+    <row r="24" spans="1:5">
+      <c r="A24" s="16" t="s">
+        <v>40</v>
+      </c>
+      <c r="B24" s="16" t="s">
+        <v>106</v>
+      </c>
+      <c r="C24" s="16" t="s">
+        <v>107</v>
+      </c>
+      <c r="D24" s="18"/>
+      <c r="E24" s="16"/>
+    </row>
+    <row r="25" spans="1:5">
+      <c r="A25" s="16"/>
+      <c r="B25" s="16"/>
+      <c r="C25" s="16"/>
+      <c r="D25" s="18"/>
+      <c r="E25" s="16"/>
+    </row>
+  </sheetData>
+  <mergeCells count="6">
+    <mergeCell ref="A5:E5"/>
+    <mergeCell ref="A4:E4"/>
+    <mergeCell ref="A17:E17"/>
+    <mergeCell ref="A18:E18"/>
+    <mergeCell ref="D3:E3"/>
+    <mergeCell ref="D16:E16"/>
+  </mergeCells>
+  <phoneticPr fontId="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5D96E6D0-45A8-48AB-B2B0-CEB4F2926A27}">
+  <dimension ref="A1:D30"/>
+  <sheetFormatPr defaultRowHeight="18.75"/>
+  <cols>
+    <col min="2" max="2" width="26" customWidth="1"/>
+    <col min="3" max="3" width="45.25" customWidth="1"/>
+    <col min="4" max="4" width="46.75" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" s="31" customFormat="1">
+      <c r="A1" s="34" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4">
+      <c r="A3" s="13" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4">
+      <c r="A4" s="32" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4">
+      <c r="A5" s="33" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4">
+      <c r="A7" s="13" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4">
+      <c r="B8" s="37" t="s">
+        <v>118</v>
+      </c>
+      <c r="C8" s="37" t="s">
+        <v>128</v>
+      </c>
+      <c r="D8" s="37" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4">
+      <c r="B9" s="16" t="s">
+        <v>119</v>
+      </c>
+      <c r="C9" s="16" t="s">
+        <v>102</v>
+      </c>
+      <c r="D9" s="16" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4">
+      <c r="B10" s="16" t="s">
+        <v>122</v>
+      </c>
+      <c r="C10" s="35">
+        <v>8765</v>
+      </c>
+      <c r="D10" s="16" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4">
+      <c r="B11" s="16" t="s">
+        <v>123</v>
+      </c>
+      <c r="C11" s="16" t="s">
+        <v>129</v>
+      </c>
+      <c r="D11" s="16" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4">
+      <c r="B12" s="16" t="s">
+        <v>125</v>
+      </c>
+      <c r="C12" s="16" t="s">
+        <v>130</v>
+      </c>
+      <c r="D12" s="16" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4">
+      <c r="B13" s="16" t="s">
+        <v>127</v>
+      </c>
+      <c r="C13" s="35">
+        <v>10</v>
+      </c>
+      <c r="D13" s="16" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4">
+      <c r="B14" s="16" t="s">
+        <v>132</v>
+      </c>
+      <c r="C14" s="35">
+        <v>10</v>
+      </c>
+      <c r="D14" s="16" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4">
+      <c r="B15" s="16" t="s">
+        <v>67</v>
+      </c>
+      <c r="C15" s="35">
+        <v>10</v>
+      </c>
+      <c r="D15" s="16" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4">
+      <c r="B16" s="16" t="s">
+        <v>135</v>
+      </c>
+      <c r="C16" s="36" t="s">
+        <v>137</v>
+      </c>
+      <c r="D16" s="16" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4">
+      <c r="B17" s="16" t="s">
+        <v>136</v>
+      </c>
+      <c r="C17" s="35">
+        <v>60</v>
+      </c>
+      <c r="D17" s="16" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" s="31" customFormat="1">
+      <c r="A19" s="34" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4">
+      <c r="A21" s="13" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4">
+      <c r="A22" s="32" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4">
+      <c r="A23" s="33" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4">
+      <c r="A25" s="13" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4">
+      <c r="B26" s="37" t="s">
+        <v>118</v>
+      </c>
+      <c r="C26" s="37" t="s">
+        <v>128</v>
+      </c>
+      <c r="D26" s="37" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4">
+      <c r="B27" s="16" t="s">
+        <v>122</v>
+      </c>
+      <c r="C27" s="35">
+        <v>5000</v>
+      </c>
+      <c r="D27" s="16" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4">
+      <c r="B28" s="16" t="s">
+        <v>144</v>
+      </c>
+      <c r="C28" s="35" t="s">
+        <v>145</v>
+      </c>
+      <c r="D28" s="16" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4">
+      <c r="B29" s="16" t="s">
+        <v>147</v>
+      </c>
+      <c r="C29" s="35">
+        <v>3</v>
+      </c>
+      <c r="D29" s="16" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4">
+      <c r="B30" s="16"/>
+      <c r="C30" s="16"/>
+      <c r="D30" s="16"/>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/設計書.xlsx
+++ b/設計書.xlsx
@@ -8,15 +8,16 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\ikura\次世代開発\ソース\CounterServer\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{20EBFCCA-08EB-4B70-98BA-81E7B9A85F5A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FBFAF41B-8F9B-4620-98BD-227D08F87B58}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="レイアウト" sheetId="1" r:id="rId1"/>
     <sheet name="設計書_距離" sheetId="2" r:id="rId2"/>
     <sheet name="テーブル" sheetId="3" r:id="rId3"/>
     <sheet name="環境設定ファイル" sheetId="4" r:id="rId4"/>
+    <sheet name="サービスの自動起動" sheetId="5" r:id="rId5"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -28,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="256" uniqueCount="149">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="303" uniqueCount="192">
   <si>
     <t>Home</t>
     <phoneticPr fontId="1"/>
@@ -1294,6 +1295,257 @@
     </rPh>
     <rPh sb="8" eb="10">
       <t>ダイスウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>jisedai_app.service ファイルの作成</t>
+    <rPh sb="25" eb="27">
+      <t>サクセイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ファイル作成場所：</t>
+    <rPh sb="4" eb="6">
+      <t>サクセイ</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>バショ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>/etc/systemd/system/</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>└jisedai_app.service</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>systemdの設定をリロード</t>
+    <rPh sb="8" eb="10">
+      <t>セッテイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>新しいサービスファイルを追加したことをsystemdに通知して再読み込みさせる</t>
+    <rPh sb="0" eb="1">
+      <t>アタラ</t>
+    </rPh>
+    <rPh sb="12" eb="14">
+      <t>ツイカ</t>
+    </rPh>
+    <rPh sb="27" eb="29">
+      <t>ツウチ</t>
+    </rPh>
+    <rPh sb="31" eb="33">
+      <t>サイヨ</t>
+    </rPh>
+    <rPh sb="34" eb="35">
+      <t>コ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>コマンド：</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>sudo systemctl daemon-reload</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>自動起動の有効化の設定</t>
+    <rPh sb="0" eb="4">
+      <t>ジドウキドウ</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>ユウコウ</t>
+    </rPh>
+    <rPh sb="7" eb="8">
+      <t>カ</t>
+    </rPh>
+    <rPh sb="9" eb="11">
+      <t>セッテイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ラズパイが起動したときに、自動でこのサービスが始まるように設定</t>
+    <rPh sb="5" eb="7">
+      <t>キドウ</t>
+    </rPh>
+    <rPh sb="13" eb="15">
+      <t>ジドウ</t>
+    </rPh>
+    <rPh sb="23" eb="24">
+      <t>ハジ</t>
+    </rPh>
+    <rPh sb="29" eb="31">
+      <t>セッテイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>sudo systemctl enable jisedai_app.service</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>サービスを今すぐ動かす場合</t>
+    <rPh sb="5" eb="6">
+      <t>イマ</t>
+    </rPh>
+    <rPh sb="8" eb="9">
+      <t>ウゴ</t>
+    </rPh>
+    <rPh sb="11" eb="13">
+      <t>バアイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>sudo systemctl start jisedai_app.service</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>正しく起動しているかの確認</t>
+    <rPh sb="0" eb="1">
+      <t>タダ</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>キドウ</t>
+    </rPh>
+    <rPh sb="11" eb="13">
+      <t>カクニン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>sudo systemctl status jisedai_app.service</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>jisedai_app.service の内容</t>
+    <rPh sb="21" eb="23">
+      <t>ナイヨウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Description=Jisedai Flask App Service</t>
+  </si>
+  <si>
+    <t>After=network.target</t>
+  </si>
+  <si>
+    <t>[Service]</t>
+  </si>
+  <si>
+    <t>Type=simple</t>
+  </si>
+  <si>
+    <t>User=user01</t>
+  </si>
+  <si>
+    <t>WorkingDirectory=/home/user01/jisedai</t>
+  </si>
+  <si>
+    <t>ExecStart=/bin/bash /home/user01/jisedai/CounterServer/start.sh</t>
+  </si>
+  <si>
+    <t>Restart=always</t>
+  </si>
+  <si>
+    <t>[Install]</t>
+  </si>
+  <si>
+    <t>WantedBy=multi-user.target</t>
+  </si>
+  <si>
+    <t>start.sh の内容</t>
+    <rPh sb="10" eb="12">
+      <t>ナイヨウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>#!/bin/bash</t>
+  </si>
+  <si>
+    <t>#cd /home/user01/jisedai</t>
+  </si>
+  <si>
+    <t>#source ./jisedaienv/bin/activate</t>
+  </si>
+  <si>
+    <t>cd /home/user01/jisedai/CounterServer</t>
+  </si>
+  <si>
+    <t>./../jisedaienv/bin/python main.py &amp;</t>
+  </si>
+  <si>
+    <t>cd /home/user01/jisedai/CounterServer/web</t>
+  </si>
+  <si>
+    <t>./../../jisedaienv/bin/python app.py</t>
+  </si>
+  <si>
+    <t>※Python.exeは、仮想環境のものを使うので上記のような指定となっている</t>
+    <rPh sb="13" eb="17">
+      <t>カソウカンキョウ</t>
+    </rPh>
+    <rPh sb="21" eb="22">
+      <t>ツカ</t>
+    </rPh>
+    <rPh sb="25" eb="27">
+      <t>ジョウキ</t>
+    </rPh>
+    <rPh sb="31" eb="33">
+      <t>シテイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>サービス関係のその他コマンド</t>
+    <rPh sb="4" eb="6">
+      <t>カンケイ</t>
+    </rPh>
+    <rPh sb="9" eb="10">
+      <t>ホカ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t># 当ファイルを修正したら以下を実行</t>
+  </si>
+  <si>
+    <t># サービスを止めたい場合</t>
+  </si>
+  <si>
+    <t># サービスを起動したい場合</t>
+  </si>
+  <si>
+    <t>sudo systemctl restart jisedai_app.service</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>sudo systemctl reset-failed jisedai_app.service</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>sudo systemctl stop jisedai_app.service</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t># エラー発生時のエラーに対する安全装置をクリア</t>
+    <rPh sb="5" eb="8">
+      <t>ハッセイジ</t>
+    </rPh>
+    <rPh sb="13" eb="14">
+      <t>タイ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -1520,7 +1772,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="38">
+  <cellXfs count="35">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
@@ -1543,9 +1795,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1560,21 +1809,8 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
@@ -1591,8 +1827,19 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -5636,62 +5883,62 @@
     <col min="5" max="5" width="20.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" s="20" customFormat="1" ht="35.25" customHeight="1">
-      <c r="A1" s="21" t="s">
+    <row r="1" spans="1:5" s="19" customFormat="1" ht="35.25" customHeight="1">
+      <c r="A1" s="20" t="s">
         <v>101</v>
       </c>
-      <c r="B1" s="19" t="s">
+      <c r="B1" s="18" t="s">
         <v>102</v>
       </c>
-      <c r="D1" s="24"/>
+      <c r="D1" s="22"/>
     </row>
     <row r="3" spans="1:5">
-      <c r="A3" s="22" t="s">
+      <c r="A3" s="21" t="s">
         <v>91</v>
       </c>
       <c r="B3" s="16" t="s">
         <v>55</v>
       </c>
-      <c r="C3" s="22" t="s">
+      <c r="C3" s="21" t="s">
         <v>94</v>
       </c>
-      <c r="D3" s="25" t="s">
+      <c r="D3" s="33" t="s">
         <v>92</v>
       </c>
-      <c r="E3" s="26"/>
+      <c r="E3" s="34"/>
     </row>
     <row r="4" spans="1:5">
-      <c r="A4" s="23" t="s">
+      <c r="A4" s="32" t="s">
         <v>108</v>
       </c>
-      <c r="B4" s="23"/>
-      <c r="C4" s="23"/>
-      <c r="D4" s="23"/>
-      <c r="E4" s="23"/>
+      <c r="B4" s="32"/>
+      <c r="C4" s="32"/>
+      <c r="D4" s="32"/>
+      <c r="E4" s="32"/>
     </row>
     <row r="5" spans="1:5" ht="48" customHeight="1">
-      <c r="A5" s="17" t="s">
+      <c r="A5" s="31" t="s">
         <v>109</v>
       </c>
-      <c r="B5" s="17"/>
-      <c r="C5" s="17"/>
-      <c r="D5" s="17"/>
-      <c r="E5" s="17"/>
+      <c r="B5" s="31"/>
+      <c r="C5" s="31"/>
+      <c r="D5" s="31"/>
+      <c r="E5" s="31"/>
     </row>
     <row r="6" spans="1:5">
-      <c r="A6" s="22" t="s">
+      <c r="A6" s="21" t="s">
         <v>93</v>
       </c>
-      <c r="B6" s="22" t="s">
+      <c r="B6" s="21" t="s">
         <v>94</v>
       </c>
-      <c r="C6" s="22" t="s">
+      <c r="C6" s="21" t="s">
         <v>96</v>
       </c>
-      <c r="D6" s="22" t="s">
+      <c r="D6" s="21" t="s">
         <v>98</v>
       </c>
-      <c r="E6" s="22" t="s">
+      <c r="E6" s="21" t="s">
         <v>110</v>
       </c>
     </row>
@@ -5705,7 +5952,7 @@
       <c r="C7" s="16" t="s">
         <v>97</v>
       </c>
-      <c r="D7" s="18" t="s">
+      <c r="D7" s="17" t="s">
         <v>99</v>
       </c>
       <c r="E7" s="16"/>
@@ -5720,7 +5967,7 @@
       <c r="C8" s="16" t="s">
         <v>105</v>
       </c>
-      <c r="D8" s="18"/>
+      <c r="D8" s="17"/>
       <c r="E8" s="16"/>
     </row>
     <row r="9" spans="1:5">
@@ -5733,7 +5980,7 @@
       <c r="C9" s="16" t="s">
         <v>105</v>
       </c>
-      <c r="D9" s="18"/>
+      <c r="D9" s="17"/>
       <c r="E9" s="16"/>
     </row>
     <row r="10" spans="1:5">
@@ -5746,7 +5993,7 @@
       <c r="C10" s="16" t="s">
         <v>105</v>
       </c>
-      <c r="D10" s="18"/>
+      <c r="D10" s="17"/>
       <c r="E10" s="16"/>
     </row>
     <row r="11" spans="1:5">
@@ -5759,73 +6006,66 @@
       <c r="C11" s="16" t="s">
         <v>107</v>
       </c>
-      <c r="D11" s="18"/>
+      <c r="D11" s="17"/>
       <c r="E11" s="16"/>
     </row>
     <row r="12" spans="1:5">
       <c r="A12" s="16"/>
       <c r="B12" s="16"/>
       <c r="C12" s="16"/>
-      <c r="D12" s="18"/>
+      <c r="D12" s="17"/>
       <c r="E12" s="16"/>
     </row>
-    <row r="13" spans="1:5">
-      <c r="A13" s="27"/>
-      <c r="B13" s="27"/>
-      <c r="C13" s="27"/>
-      <c r="D13" s="28"/>
-      <c r="E13" s="27"/>
-    </row>
-    <row r="14" spans="1:5" s="29" customFormat="1">
-      <c r="D14" s="30"/>
+    <row r="14" spans="1:5" s="23" customFormat="1">
+      <c r="D14" s="24"/>
     </row>
     <row r="16" spans="1:5">
-      <c r="A16" s="22" t="s">
+      <c r="A16" s="21" t="s">
         <v>91</v>
       </c>
       <c r="B16" s="16" t="s">
         <v>54</v>
       </c>
-      <c r="C16" s="22" t="s">
+      <c r="C16" s="21" t="s">
         <v>94</v>
       </c>
-      <c r="D16" s="25" t="s">
+      <c r="D16" s="33" t="s">
         <v>111</v>
       </c>
-      <c r="E16" s="26"/>
+      <c r="E16" s="34"/>
     </row>
     <row r="17" spans="1:5">
-      <c r="A17" s="23" t="s">
+      <c r="A17" s="32" t="s">
         <v>108</v>
       </c>
-      <c r="B17" s="23"/>
-      <c r="C17" s="23"/>
-      <c r="D17" s="23"/>
-      <c r="E17" s="23"/>
+      <c r="B17" s="32"/>
+      <c r="C17" s="32"/>
+      <c r="D17" s="32"/>
+      <c r="E17" s="32"/>
     </row>
     <row r="18" spans="1:5" ht="48" customHeight="1">
-      <c r="A18" s="17" t="s">
+      <c r="A18" s="31" t="s">
         <v>112</v>
       </c>
-      <c r="B18" s="17"/>
-      <c r="C18" s="17"/>
-      <c r="D18" s="17"/>
-      <c r="E18" s="17"/>
+      <c r="B18" s="31"/>
+      <c r="C18" s="31"/>
+      <c r="D18" s="31"/>
+      <c r="E18" s="31"/>
     </row>
     <row r="19" spans="1:5">
-      <c r="A19" s="22" t="s">
+      <c r="A19" s="21" t="s">
         <v>93</v>
       </c>
-      <c r="B19" s="22" t="s">
+      <c r="B19" s="21" t="s">
         <v>94</v>
       </c>
-      <c r="C19" s="22" t="s">
+      <c r="C19" s="21" t="s">
         <v>96</v>
       </c>
-      <c r="D19" s="22" t="s">
+      <c r="D19" s="21" t="s">
         <v>98</v>
       </c>
-      <c r="E19" s="22" t="s">
+      <c r="E19" s="21" t="s">
         <v>110</v>
       </c>
     </row>
@@ -5839,7 +6079,7 @@
       <c r="C20" s="16" t="s">
         <v>97</v>
       </c>
-      <c r="D20" s="18" t="s">
+      <c r="D20" s="17" t="s">
         <v>99</v>
       </c>
       <c r="E20" s="16"/>
@@ -5854,7 +6094,7 @@
       <c r="C21" s="16" t="s">
         <v>105</v>
       </c>
-      <c r="D21" s="18"/>
+      <c r="D21" s="17"/>
       <c r="E21" s="16"/>
     </row>
     <row r="22" spans="1:5">
@@ -5867,7 +6107,7 @@
       <c r="C22" s="16" t="s">
         <v>105</v>
       </c>
-      <c r="D22" s="18"/>
+      <c r="D22" s="17"/>
       <c r="E22" s="16"/>
     </row>
     <row r="23" spans="1:5">
@@ -5880,7 +6120,7 @@
       <c r="C23" s="16" t="s">
         <v>105</v>
       </c>
-      <c r="D23" s="18"/>
+      <c r="D23" s="17"/>
       <c r="E23" s="16"/>
     </row>
     <row r="24" spans="1:5">
@@ -5893,14 +6133,14 @@
       <c r="C24" s="16" t="s">
         <v>107</v>
       </c>
-      <c r="D24" s="18"/>
+      <c r="D24" s="17"/>
       <c r="E24" s="16"/>
     </row>
     <row r="25" spans="1:5">
       <c r="A25" s="16"/>
       <c r="B25" s="16"/>
       <c r="C25" s="16"/>
-      <c r="D25" s="18"/>
+      <c r="D25" s="17"/>
       <c r="E25" s="16"/>
     </row>
   </sheetData>
@@ -5928,8 +6168,8 @@
     <col min="4" max="4" width="46.75" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" s="31" customFormat="1">
-      <c r="A1" s="34" t="s">
+    <row r="1" spans="1:4" s="25" customFormat="1">
+      <c r="A1" s="28" t="s">
         <v>113</v>
       </c>
     </row>
@@ -5939,12 +6179,12 @@
       </c>
     </row>
     <row r="4" spans="1:4">
-      <c r="A4" s="32" t="s">
+      <c r="A4" s="26" t="s">
         <v>115</v>
       </c>
     </row>
     <row r="5" spans="1:4">
-      <c r="A5" s="33" t="s">
+      <c r="A5" s="27" t="s">
         <v>116</v>
       </c>
     </row>
@@ -5954,13 +6194,13 @@
       </c>
     </row>
     <row r="8" spans="1:4">
-      <c r="B8" s="37" t="s">
+      <c r="B8" s="30" t="s">
         <v>118</v>
       </c>
-      <c r="C8" s="37" t="s">
+      <c r="C8" s="30" t="s">
         <v>128</v>
       </c>
-      <c r="D8" s="37" t="s">
+      <c r="D8" s="30" t="s">
         <v>121</v>
       </c>
     </row>
@@ -5979,7 +6219,7 @@
       <c r="B10" s="16" t="s">
         <v>122</v>
       </c>
-      <c r="C10" s="35">
+      <c r="C10" s="29">
         <v>8765</v>
       </c>
       <c r="D10" s="16" t="s">
@@ -6012,7 +6252,7 @@
       <c r="B13" s="16" t="s">
         <v>127</v>
       </c>
-      <c r="C13" s="35">
+      <c r="C13" s="29">
         <v>10</v>
       </c>
       <c r="D13" s="16" t="s">
@@ -6023,7 +6263,7 @@
       <c r="B14" s="16" t="s">
         <v>132</v>
       </c>
-      <c r="C14" s="35">
+      <c r="C14" s="29">
         <v>10</v>
       </c>
       <c r="D14" s="16" t="s">
@@ -6034,7 +6274,7 @@
       <c r="B15" s="16" t="s">
         <v>67</v>
       </c>
-      <c r="C15" s="35">
+      <c r="C15" s="29">
         <v>10</v>
       </c>
       <c r="D15" s="16" t="s">
@@ -6045,7 +6285,7 @@
       <c r="B16" s="16" t="s">
         <v>135</v>
       </c>
-      <c r="C16" s="36" t="s">
+      <c r="C16" s="16" t="s">
         <v>137</v>
       </c>
       <c r="D16" s="16" t="s">
@@ -6056,15 +6296,15 @@
       <c r="B17" s="16" t="s">
         <v>136</v>
       </c>
-      <c r="C17" s="35">
+      <c r="C17" s="29">
         <v>60</v>
       </c>
       <c r="D17" s="16" t="s">
         <v>139</v>
       </c>
     </row>
-    <row r="19" spans="1:4" s="31" customFormat="1">
-      <c r="A19" s="34" t="s">
+    <row r="19" spans="1:4" s="25" customFormat="1">
+      <c r="A19" s="28" t="s">
         <v>140</v>
       </c>
     </row>
@@ -6074,12 +6314,12 @@
       </c>
     </row>
     <row r="22" spans="1:4">
-      <c r="A22" s="32" t="s">
+      <c r="A22" s="26" t="s">
         <v>141</v>
       </c>
     </row>
     <row r="23" spans="1:4">
-      <c r="A23" s="33" t="s">
+      <c r="A23" s="27" t="s">
         <v>116</v>
       </c>
     </row>
@@ -6089,13 +6329,13 @@
       </c>
     </row>
     <row r="26" spans="1:4">
-      <c r="B26" s="37" t="s">
+      <c r="B26" s="30" t="s">
         <v>118</v>
       </c>
-      <c r="C26" s="37" t="s">
+      <c r="C26" s="30" t="s">
         <v>128</v>
       </c>
-      <c r="D26" s="37" t="s">
+      <c r="D26" s="30" t="s">
         <v>121</v>
       </c>
     </row>
@@ -6103,7 +6343,7 @@
       <c r="B27" s="16" t="s">
         <v>122</v>
       </c>
-      <c r="C27" s="35">
+      <c r="C27" s="29">
         <v>5000</v>
       </c>
       <c r="D27" s="16" t="s">
@@ -6114,7 +6354,7 @@
       <c r="B28" s="16" t="s">
         <v>144</v>
       </c>
-      <c r="C28" s="35" t="s">
+      <c r="C28" s="29" t="s">
         <v>145</v>
       </c>
       <c r="D28" s="16" t="s">
@@ -6125,7 +6365,7 @@
       <c r="B29" s="16" t="s">
         <v>147</v>
       </c>
-      <c r="C29" s="35">
+      <c r="C29" s="29">
         <v>3</v>
       </c>
       <c r="D29" s="16" t="s">
@@ -6141,4 +6381,254 @@
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{57ADDA96-755C-4460-8ED7-811E108D3F2F}">
+  <dimension ref="A1:C70"/>
+  <sheetFormatPr defaultRowHeight="18.75"/>
+  <cols>
+    <col min="1" max="1" width="3.25" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3">
+      <c r="A1" s="13" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3">
+      <c r="B3" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3">
+      <c r="C4" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3">
+      <c r="C5" s="26" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3">
+      <c r="A7" s="13" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3">
+      <c r="B8" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3">
+      <c r="B10" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3">
+      <c r="C11" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3">
+      <c r="A13" s="13" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3">
+      <c r="B14" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3">
+      <c r="B16" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3">
+      <c r="C17" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3">
+      <c r="A19" s="13" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3">
+      <c r="B21" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3">
+      <c r="C22" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3">
+      <c r="A24" s="13" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3">
+      <c r="B26" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3">
+      <c r="C27" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3">
+      <c r="A29" s="13" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3">
+      <c r="B31" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3">
+      <c r="B32" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2">
+      <c r="B34" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2">
+      <c r="B35" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2">
+      <c r="B36" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2">
+      <c r="B37" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2">
+      <c r="B38" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="39" spans="1:2">
+      <c r="B39" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="41" spans="1:2">
+      <c r="B41" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="42" spans="1:2">
+      <c r="B42" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="44" spans="1:2">
+      <c r="A44" s="13" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="46" spans="1:2">
+      <c r="B46" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="47" spans="1:2">
+      <c r="B47" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="48" spans="1:2">
+      <c r="B48" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="50" spans="1:2">
+      <c r="B50" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="51" spans="1:2">
+      <c r="B51" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="53" spans="1:2">
+      <c r="B53" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="54" spans="1:2">
+      <c r="B54" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="56" spans="1:2">
+      <c r="B56" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="58" spans="1:2">
+      <c r="A58" s="13" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="60" spans="1:2">
+      <c r="B60" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="61" spans="1:2">
+      <c r="B61" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="63" spans="1:2">
+      <c r="B63" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="64" spans="1:2">
+      <c r="B64" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="66" spans="2:2">
+      <c r="B66" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="67" spans="2:2">
+      <c r="B67" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="69" spans="2:2">
+      <c r="B69" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="70" spans="2:2">
+      <c r="B70" t="s">
+        <v>161</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
 </file>